--- a/notebooks/data/backtest/ibkr_b1_sizing_export.xlsx
+++ b/notebooks/data/backtest/ibkr_b1_sizing_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q117"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,12 +518,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASTX</t>
+          <t>NVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -532,57 +532,57 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0284359111448349</v>
+        <v>0.02583261238119269</v>
       </c>
       <c r="E2" t="n">
-        <v>2665866.669828272</v>
+        <v>2421807.410736815</v>
       </c>
       <c r="F2" t="n">
-        <v>1774272.465872328</v>
+        <v>1609120.360153991</v>
       </c>
       <c r="G2" t="n">
-        <v>-891594.2039559438</v>
+        <v>-812687.0505828238</v>
       </c>
       <c r="H2" t="n">
-        <v>891594.2039559438</v>
+        <v>812687.0505828238</v>
       </c>
       <c r="I2" t="n">
-        <v>26.38999938964844</v>
+        <v>108.3899993896484</v>
       </c>
       <c r="J2" t="n">
-        <v>33785.30597108215</v>
+        <v>7497.804734376978</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01214047573545693</v>
+        <v>0.0292696463419954</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002816765367176752</v>
+        <v>0.01807555000799013</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002823677891440213</v>
+        <v>0.01209323344254351</v>
       </c>
       <c r="N2" t="n">
-        <v>2782865.079365079</v>
+        <v>256163.1475409836</v>
       </c>
       <c r="O2" t="n">
-        <v>73439807.74591839</v>
+        <v>27765523.40561764</v>
       </c>
       <c r="P2" t="n">
-        <v>316531229.17</v>
+        <v>44960571.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>11965000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CWVX</t>
+          <t>BEX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -591,57 +591,57 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02574662518285399</v>
+        <v>0.02220753014017379</v>
       </c>
       <c r="E3" t="n">
-        <v>2413746.110892562</v>
+        <v>2081955.950641292</v>
       </c>
       <c r="F3" t="n">
-        <v>1606473.164105752</v>
+        <v>1382608.973603572</v>
       </c>
       <c r="G3" t="n">
-        <v>-807272.9467868098</v>
+        <v>-699346.97703772</v>
       </c>
       <c r="H3" t="n">
-        <v>807272.9467868098</v>
+        <v>699346.97703772</v>
       </c>
       <c r="I3" t="n">
-        <v>37.90999984741211</v>
+        <v>63.84999847412109</v>
       </c>
       <c r="J3" t="n">
-        <v>21294.45924653354</v>
+        <v>10952.96779562447</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01294259967576341</v>
+        <v>0.01145520236426542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006590935047573982</v>
+        <v>0.007681469416166737</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006609122107068801</v>
+        <v>0.006500277623516008</v>
       </c>
       <c r="N3" t="n">
-        <v>1645300</v>
+        <v>956156.6393442623</v>
       </c>
       <c r="O3" t="n">
-        <v>62373322.74894714</v>
+        <v>61050599.9631519</v>
       </c>
       <c r="P3" t="n">
-        <v>122482309.56</v>
+        <v>91043384.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3221980</v>
+        <v>1685000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IRE</t>
+          <t>LUNL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,57 +650,57 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0256333102763948</v>
+        <v>0.02128130482355588</v>
       </c>
       <c r="E4" t="n">
-        <v>2403122.838412012</v>
+        <v>1995122.327208363</v>
       </c>
       <c r="F4" t="n">
-        <v>1600208.425310772</v>
+        <v>1327857.334830984</v>
       </c>
       <c r="G4" t="n">
-        <v>-802914.4131012403</v>
+        <v>-667264.9923773791</v>
       </c>
       <c r="H4" t="n">
-        <v>802914.4131012403</v>
+        <v>667264.9923773791</v>
       </c>
       <c r="I4" t="n">
-        <v>36.93999862670898</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="J4" t="n">
-        <v>21735.6373294693</v>
+        <v>22316.55521372807</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003806866358408321</v>
+        <v>0.0396820141456016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001660183224988608</v>
+        <v>0.02102946714079354</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001658262480984655</v>
+        <v>0.01703553833109013</v>
       </c>
       <c r="N4" t="n">
-        <v>5709587.698412699</v>
+        <v>562384.6393442623</v>
       </c>
       <c r="O4" t="n">
-        <v>210912161.7384396</v>
+        <v>16815300.50186073</v>
       </c>
       <c r="P4" t="n">
-        <v>483630000</v>
+        <v>31730000</v>
       </c>
       <c r="Q4" t="n">
-        <v>13107477</v>
+        <v>1310000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SNDU</t>
+          <t>ASTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>ASTS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -709,57 +709,57 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02557234935292766</v>
+        <v>0.02104975473100235</v>
       </c>
       <c r="E5" t="n">
-        <v>2397407.751836969</v>
+        <v>1973414.50603147</v>
       </c>
       <c r="F5" t="n">
-        <v>1596135.107506431</v>
+        <v>1313409.654515928</v>
       </c>
       <c r="G5" t="n">
-        <v>-801272.6443305376</v>
+        <v>-660004.8515155417</v>
       </c>
       <c r="H5" t="n">
-        <v>801272.6443305376</v>
+        <v>660004.8515155417</v>
       </c>
       <c r="I5" t="n">
-        <v>118</v>
+        <v>31.61000061035156</v>
       </c>
       <c r="J5" t="n">
-        <v>6790.446138394387</v>
+        <v>20879.62159986182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01144356859664964</v>
+        <v>0.00704488374736403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006559335189382712</v>
+        <v>0.002085117646199363</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004920613143764048</v>
+        <v>0.001745058219796224</v>
       </c>
       <c r="N5" t="n">
-        <v>593385.3658536585</v>
+        <v>2963799.31147541</v>
       </c>
       <c r="O5" t="n">
-        <v>70019473.17073171</v>
+        <v>93685698.04469724</v>
       </c>
       <c r="P5" t="n">
-        <v>122157600</v>
+        <v>316531229.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>1380000</v>
+        <v>11965000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEBX</t>
+          <t>LITX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -768,57 +768,57 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02557165069465555</v>
+        <v>0.02029790400999076</v>
       </c>
       <c r="E6" t="n">
-        <v>2397342.252623958</v>
+        <v>1902928.500936634</v>
       </c>
       <c r="F6" t="n">
-        <v>1597961.708234509</v>
+        <v>1264361.889884072</v>
       </c>
       <c r="G6" t="n">
-        <v>-799380.5443894489</v>
+        <v>-638566.6110525617</v>
       </c>
       <c r="H6" t="n">
-        <v>799380.5443894489</v>
+        <v>638566.6110525617</v>
       </c>
       <c r="I6" t="n">
-        <v>85.37000274658203</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="J6" t="n">
-        <v>9363.716981038211</v>
+        <v>10786.59802065947</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01021770639401757</v>
+        <v>0.002162583012113754</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003841706247635337</v>
+        <v>0.001145333075408179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003837588926655005</v>
+        <v>0.0008605183901603085</v>
       </c>
       <c r="N6" t="n">
-        <v>916420.6349206349</v>
+        <v>4987830.737704918</v>
       </c>
       <c r="O6" t="n">
-        <v>78234832.12019905</v>
+        <v>295279583.477544</v>
       </c>
       <c r="P6" t="n">
-        <v>208079559.67</v>
+        <v>557537911.6900001</v>
       </c>
       <c r="Q6" t="n">
-        <v>2440000</v>
+        <v>12535000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SNXX</t>
+          <t>IRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,52 +827,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0254237725257897</v>
+        <v>0.01960558290074035</v>
       </c>
       <c r="E7" t="n">
-        <v>2383478.674292785</v>
+        <v>1838023.396944408</v>
       </c>
       <c r="F7" t="n">
-        <v>1586328.616000884</v>
+        <v>1224121.126755895</v>
       </c>
       <c r="G7" t="n">
-        <v>-797150.0582919011</v>
+        <v>-613902.2701885132</v>
       </c>
       <c r="H7" t="n">
-        <v>797150.0582919011</v>
+        <v>613902.2701885132</v>
       </c>
       <c r="I7" t="n">
-        <v>195.8899993896484</v>
+        <v>29.56999969482422</v>
       </c>
       <c r="J7" t="n">
-        <v>4069.375980272863</v>
+        <v>20760.98331160847</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004068209114579205</v>
+        <v>0.00359817474841861</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003270929306169334</v>
+        <v>0.001269363501413298</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003256803505620538</v>
+        <v>0.001583903852099719</v>
       </c>
       <c r="N7" t="n">
-        <v>10002868.25396825</v>
+        <v>5769865.213114754</v>
       </c>
       <c r="O7" t="n">
-        <v>1959461856.164575</v>
+        <v>170614912.5909802</v>
       </c>
       <c r="P7" t="n">
-        <v>2437075166.34</v>
+        <v>483630000</v>
       </c>
       <c r="Q7" t="n">
-        <v>12495000</v>
+        <v>13107477</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NBIG</t>
+          <t>NEBX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -886,52 +886,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02531056452336683</v>
+        <v>0.01895140010441564</v>
       </c>
       <c r="E8" t="n">
-        <v>2372865.424065641</v>
+        <v>1776693.759788966</v>
       </c>
       <c r="F8" t="n">
-        <v>1584276.050830133</v>
+        <v>1184265.030282809</v>
       </c>
       <c r="G8" t="n">
-        <v>-788589.3732355071</v>
+        <v>-592428.7295061573</v>
       </c>
       <c r="H8" t="n">
-        <v>788589.3732355071</v>
+        <v>592428.7295061573</v>
       </c>
       <c r="I8" t="n">
-        <v>19.29999923706055</v>
+        <v>93.69000244140625</v>
       </c>
       <c r="J8" t="n">
-        <v>40859.55463258411</v>
+        <v>6323.286520102958</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03241078359024308</v>
+        <v>0.006907201149873874</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01848848552822796</v>
+        <v>0.002847126024515377</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01848848625908783</v>
+        <v>0.002591510868894655</v>
       </c>
       <c r="N8" t="n">
-        <v>1260677.777777778</v>
+        <v>915462.9180327869</v>
       </c>
       <c r="O8" t="n">
-        <v>24331080.1492903</v>
+        <v>85769723.0255087</v>
       </c>
       <c r="P8" t="n">
-        <v>42653000</v>
+        <v>208079559.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2210000</v>
+        <v>2440000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRWG</t>
+          <t>CWVX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -945,57 +945,57 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02529215146605804</v>
+        <v>0.01879125246923219</v>
       </c>
       <c r="E9" t="n">
-        <v>2371139.199942941</v>
+        <v>1761679.918990518</v>
       </c>
       <c r="F9" t="n">
-        <v>1579968.295724409</v>
+        <v>1172489.310632485</v>
       </c>
       <c r="G9" t="n">
-        <v>-791170.9042185323</v>
+        <v>-589190.6083580325</v>
       </c>
       <c r="H9" t="n">
-        <v>791170.9042185323</v>
+        <v>589190.6083580325</v>
       </c>
       <c r="I9" t="n">
-        <v>46.52999877929688</v>
+        <v>38.22999954223633</v>
       </c>
       <c r="J9" t="n">
-        <v>17003.45852084047</v>
+        <v>15411.73464328969</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006678953317333394</v>
+        <v>0.009246730065526464</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005217770143091214</v>
+        <v>0.004810413932221026</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005217769495403304</v>
+        <v>0.004783311703762807</v>
       </c>
       <c r="N9" t="n">
-        <v>2545826.825396826</v>
+        <v>1666722.672131147</v>
       </c>
       <c r="O9" t="n">
-        <v>118457319.0780155</v>
+        <v>63718806.99260867</v>
       </c>
       <c r="P9" t="n">
-        <v>151630080</v>
+        <v>122482309.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>3258760</v>
+        <v>3221980</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LABX</t>
+          <t>CRWG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1004,52 +1004,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02284993592550201</v>
+        <v>0.01870450676305127</v>
       </c>
       <c r="E10" t="n">
-        <v>2142181.493015813</v>
+        <v>1753547.509036057</v>
       </c>
       <c r="F10" t="n">
-        <v>1426690.012382609</v>
+        <v>1168446.571753422</v>
       </c>
       <c r="G10" t="n">
-        <v>-715491.4806332041</v>
+        <v>-585100.9372826349</v>
       </c>
       <c r="H10" t="n">
-        <v>715491.4806332041</v>
+        <v>585100.9372826349</v>
       </c>
       <c r="I10" t="n">
-        <v>45.27999877929688</v>
+        <v>46.95000076293945</v>
       </c>
       <c r="J10" t="n">
-        <v>15801.49072266195</v>
+        <v>12462.2135841261</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03467315261855663</v>
+        <v>0.004852031993365018</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01014653392675193</v>
+        <v>0.003858739224319046</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01014011334207907</v>
+        <v>0.003824219514209731</v>
       </c>
       <c r="N10" t="n">
-        <v>455726.9682539682</v>
+        <v>2568452.475409836</v>
       </c>
       <c r="O10" t="n">
-        <v>20635316.56623235</v>
+        <v>120588845.6800655</v>
       </c>
       <c r="P10" t="n">
-        <v>70515851.59999999</v>
+        <v>151630080</v>
       </c>
       <c r="Q10" t="n">
-        <v>1558315</v>
+        <v>3258760</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBIL</t>
+          <t>NBIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,57 +1063,57 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0221260668860156</v>
+        <v>0.01851618953309209</v>
       </c>
       <c r="E11" t="n">
-        <v>2074318.770563963</v>
+        <v>1735892.768727383</v>
       </c>
       <c r="F11" t="n">
-        <v>1382417.913137691</v>
+        <v>1158992.546484983</v>
       </c>
       <c r="G11" t="n">
-        <v>-691900.8574262719</v>
+        <v>-576900.2222424005</v>
       </c>
       <c r="H11" t="n">
-        <v>691900.8574262719</v>
+        <v>576900.2222424005</v>
       </c>
       <c r="I11" t="n">
-        <v>27.3799991607666</v>
+        <v>21.27000045776367</v>
       </c>
       <c r="J11" t="n">
-        <v>25270.3023606265</v>
+        <v>27122.71790440083</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01273169990458972</v>
+        <v>0.02178661225433985</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0100974346130446</v>
+        <v>0.01352543132352708</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0100974338202952</v>
+        <v>0.01227272303366553</v>
       </c>
       <c r="N11" t="n">
-        <v>1984833.333333333</v>
+        <v>1244925.901639344</v>
       </c>
       <c r="O11" t="n">
-        <v>54344735.00092824</v>
+        <v>26479574.4977507</v>
       </c>
       <c r="P11" t="n">
-        <v>68522440</v>
+        <v>42653000</v>
       </c>
       <c r="Q11" t="n">
-        <v>2502646</v>
+        <v>2210000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CLSX</t>
+          <t>SNDU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLSK</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1122,57 +1122,57 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02113350477708607</v>
+        <v>0.01817991248400501</v>
       </c>
       <c r="E12" t="n">
-        <v>1981266.072851819</v>
+        <v>1704366.79537547</v>
       </c>
       <c r="F12" t="n">
-        <v>1320623.834488425</v>
+        <v>1134725.486760674</v>
       </c>
       <c r="G12" t="n">
-        <v>-660642.238363394</v>
+        <v>-569641.3086147961</v>
       </c>
       <c r="H12" t="n">
-        <v>660642.238363394</v>
+        <v>569641.3086147961</v>
       </c>
       <c r="I12" t="n">
-        <v>21.75</v>
+        <v>115.3499984741211</v>
       </c>
       <c r="J12" t="n">
-        <v>30374.35578682271</v>
+        <v>4938.372918510232</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07572194492425492</v>
+        <v>0.008158379404964639</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02576567641076719</v>
+        <v>0.004663167159593804</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02585051556325338</v>
+        <v>0.003578531100369733</v>
       </c>
       <c r="N12" t="n">
-        <v>401130.1587301588</v>
+        <v>605312.9761904762</v>
       </c>
       <c r="O12" t="n">
-        <v>8724580.952380953</v>
+        <v>69822850.87993713</v>
       </c>
       <c r="P12" t="n">
-        <v>25640399.57</v>
+        <v>122157600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1175000</v>
+        <v>1380000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OKLL</t>
+          <t>SNXX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1181,57 +1181,57 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02043469427330635</v>
+        <v>0.01783352197306301</v>
       </c>
       <c r="E13" t="n">
-        <v>1915752.58812247</v>
+        <v>1671892.684974657</v>
       </c>
       <c r="F13" t="n">
-        <v>1276955.459705508</v>
+        <v>1112731.251872765</v>
       </c>
       <c r="G13" t="n">
-        <v>-638797.1284169622</v>
+        <v>-559161.4331018919</v>
       </c>
       <c r="H13" t="n">
-        <v>638797.1284169622</v>
+        <v>559161.4331018919</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>191.5</v>
       </c>
       <c r="J13" t="n">
-        <v>58072.46621972384</v>
+        <v>2919.903044918496</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007209400669481146</v>
+        <v>0.0002887077456989736</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002394381829967248</v>
+        <v>0.0002294395514856608</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002391289529327727</v>
+        <v>0.0002336857178806319</v>
       </c>
       <c r="N13" t="n">
-        <v>8055103.174603174</v>
+        <v>10113698.32786885</v>
       </c>
       <c r="O13" t="n">
-        <v>88606134.92063493</v>
+        <v>1936773229.786885</v>
       </c>
       <c r="P13" t="n">
-        <v>266790000</v>
+        <v>2437075166.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>24285000</v>
+        <v>12495000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRCG</t>
+          <t>LABX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1240,57 +1240,57 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02014053243310829</v>
+        <v>0.01713427619499812</v>
       </c>
       <c r="E14" t="n">
-        <v>1888174.915603902</v>
+        <v>1606338.393281073</v>
       </c>
       <c r="F14" t="n">
-        <v>1256678.288311627</v>
+        <v>1069819.223848517</v>
       </c>
       <c r="G14" t="n">
-        <v>-631496.6272922748</v>
+        <v>-536519.1694325563</v>
       </c>
       <c r="H14" t="n">
-        <v>631496.6272922748</v>
+        <v>536519.1694325563</v>
       </c>
       <c r="I14" t="n">
-        <v>33.70999908447266</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="J14" t="n">
-        <v>18733.21401492271</v>
+        <v>11016.82055497719</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007013569893801744</v>
+        <v>0.02570467785402599</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00475641043493689</v>
+        <v>0.00760849025090064</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00475641072568717</v>
+        <v>0.007069700641383284</v>
       </c>
       <c r="N14" t="n">
-        <v>2670995.555555556</v>
+        <v>428592.0491803279</v>
       </c>
       <c r="O14" t="n">
-        <v>90039257.73240831</v>
+        <v>20872433.12207175</v>
       </c>
       <c r="P14" t="n">
-        <v>132767480</v>
+        <v>70515851.59999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>3938519</v>
+        <v>1558315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BMNG</t>
+          <t>NBIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1299,57 +1299,57 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.02002564302117302</v>
+        <v>0.016342412006526</v>
       </c>
       <c r="E15" t="n">
-        <v>1877404.033234971</v>
+        <v>1532101.125611813</v>
       </c>
       <c r="F15" t="n">
-        <v>1250139.070577112</v>
+        <v>1021060.056361708</v>
       </c>
       <c r="G15" t="n">
-        <v>-627264.9626578586</v>
+        <v>-511041.0692501043</v>
       </c>
       <c r="H15" t="n">
-        <v>627264.9626578586</v>
+        <v>511041.0692501043</v>
       </c>
       <c r="I15" t="n">
-        <v>28.77000045776367</v>
+        <v>30.31999969482422</v>
       </c>
       <c r="J15" t="n">
-        <v>21802.74427102379</v>
+        <v>16854.91670164303</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00895802846098313</v>
+        <v>0.008590153391671506</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01638094118863643</v>
+        <v>0.00745801038681787</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01638094600154156</v>
+        <v>0.006734838527559643</v>
       </c>
       <c r="N15" t="n">
-        <v>2433877.53968254</v>
+        <v>1962120.573770492</v>
       </c>
       <c r="O15" t="n">
-        <v>70022657.93080738</v>
+        <v>59491495.19792964</v>
       </c>
       <c r="P15" t="n">
-        <v>38292364</v>
+        <v>68522440</v>
       </c>
       <c r="Q15" t="n">
-        <v>1330982</v>
+        <v>2502646</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NVTX</t>
+          <t>CLSX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>CLSK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,57 +1358,57 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01958504291436663</v>
+        <v>0.0158372777324973</v>
       </c>
       <c r="E16" t="n">
-        <v>1836097.773221871</v>
+        <v>1484744.787421622</v>
       </c>
       <c r="F16" t="n">
-        <v>1220370.82043117</v>
+        <v>989664.8316291502</v>
       </c>
       <c r="G16" t="n">
-        <v>-615726.9527907013</v>
+        <v>-495079.9557924712</v>
       </c>
       <c r="H16" t="n">
-        <v>615726.9527907013</v>
+        <v>495079.9557924712</v>
       </c>
       <c r="I16" t="n">
-        <v>72.40000152587891</v>
+        <v>21.95999908447266</v>
       </c>
       <c r="J16" t="n">
-        <v>8504.515743285085</v>
+        <v>22544.62552061441</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03464161198894128</v>
+        <v>0.05654908427312236</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01369482055663866</v>
+        <v>0.01930858972930082</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01371696087626627</v>
+        <v>0.01918691533669311</v>
       </c>
       <c r="N16" t="n">
-        <v>245500</v>
+        <v>398673.5737704918</v>
       </c>
       <c r="O16" t="n">
-        <v>17774200.37460327</v>
+        <v>8754871.315003442</v>
       </c>
       <c r="P16" t="n">
-        <v>44960571.06</v>
+        <v>25640399.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>620000</v>
+        <v>1175000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRDU</t>
+          <t>CRCG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1417,57 +1417,57 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01950996194765882</v>
+        <v>0.01529884510337809</v>
       </c>
       <c r="E17" t="n">
-        <v>1829058.932593015</v>
+        <v>1434266.728441696</v>
       </c>
       <c r="F17" t="n">
-        <v>1216924.082327615</v>
+        <v>954578.8593976507</v>
       </c>
       <c r="G17" t="n">
-        <v>-612134.8502653998</v>
+        <v>-479687.8690440455</v>
       </c>
       <c r="H17" t="n">
-        <v>612134.8502653998</v>
+        <v>479687.8690440455</v>
       </c>
       <c r="I17" t="n">
-        <v>54.58000183105469</v>
+        <v>44.86999893188477</v>
       </c>
       <c r="J17" t="n">
-        <v>11215.36881145926</v>
+        <v>10690.61467490203</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02171606135434814</v>
+        <v>0.003741981976337002</v>
       </c>
       <c r="L17" t="n">
-        <v>0.008007833619127708</v>
+        <v>0.003612992195408435</v>
       </c>
       <c r="M17" t="n">
-        <v>0.007982571172768942</v>
+        <v>0.002714374280002718</v>
       </c>
       <c r="N17" t="n">
-        <v>516455.0158730159</v>
+        <v>2856939.114754098</v>
       </c>
       <c r="O17" t="n">
-        <v>28188115.71200658</v>
+        <v>128190855.0274762</v>
       </c>
       <c r="P17" t="n">
-        <v>76442004.09</v>
+        <v>132767480</v>
       </c>
       <c r="Q17" t="n">
-        <v>1404982</v>
+        <v>3938519</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRWU</t>
+          <t>OKLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1476,57 +1476,57 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01912122303632356</v>
+        <v>0.01522001449283847</v>
       </c>
       <c r="E18" t="n">
-        <v>1792614.659655333</v>
+        <v>1426876.358703607</v>
       </c>
       <c r="F18" t="n">
-        <v>1194478.303413981</v>
+        <v>950933.6106370266</v>
       </c>
       <c r="G18" t="n">
-        <v>-598136.3562413525</v>
+        <v>-475942.7480665799</v>
       </c>
       <c r="H18" t="n">
-        <v>598136.3562413525</v>
+        <v>475942.7480665799</v>
       </c>
       <c r="I18" t="n">
-        <v>8.710000038146973</v>
+        <v>12.68000030517578</v>
       </c>
       <c r="J18" t="n">
-        <v>68672.3712539276</v>
+        <v>37534.91613657986</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04425440578100532</v>
+        <v>0.004468782657858641</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02196833887587973</v>
+        <v>0.001783960223646238</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02885393750165025</v>
+        <v>0.001545600829177676</v>
       </c>
       <c r="N18" t="n">
-        <v>1551763.492063492</v>
+        <v>8399360.409836065</v>
       </c>
       <c r="O18" t="n">
-        <v>13515860.0750681</v>
+        <v>106503892.5600027</v>
       </c>
       <c r="P18" t="n">
-        <v>27227200</v>
+        <v>266790000</v>
       </c>
       <c r="Q18" t="n">
-        <v>2380000</v>
+        <v>24285000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RGTX</t>
+          <t>IREX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1535,57 +1535,57 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.01863004219567064</v>
+        <v>0.01514701018401169</v>
       </c>
       <c r="E19" t="n">
-        <v>1746566.455844122</v>
+        <v>1420032.204751096</v>
       </c>
       <c r="F19" t="n">
-        <v>1161843.839224061</v>
+        <v>945897.9126806132</v>
       </c>
       <c r="G19" t="n">
-        <v>-584722.6166200609</v>
+        <v>-474134.2920704828</v>
       </c>
       <c r="H19" t="n">
-        <v>584722.6166200609</v>
+        <v>474134.2920704828</v>
       </c>
       <c r="I19" t="n">
-        <v>23.81999969482422</v>
+        <v>39.95000076293945</v>
       </c>
       <c r="J19" t="n">
-        <v>24547.54929098986</v>
+        <v>11868.192315789</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0236949177640355</v>
+        <v>0.01144872655267448</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009470725892777143</v>
+        <v>0.005865831910869181</v>
       </c>
       <c r="M19" t="n">
-        <v>0.009459607601347312</v>
+        <v>0.007303588359364819</v>
       </c>
       <c r="N19" t="n">
-        <v>1035983.73015873</v>
+        <v>1036638.639344262</v>
       </c>
       <c r="O19" t="n">
-        <v>24677132.13622381</v>
+        <v>41413714.4326958</v>
       </c>
       <c r="P19" t="n">
-        <v>61740000</v>
+        <v>80829846.34999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>2594986</v>
+        <v>1624981</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRCA</t>
+          <t>APPX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,57 +1594,57 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01654441281865238</v>
+        <v>0.01473644137295423</v>
       </c>
       <c r="E20" t="n">
-        <v>1551038.701748661</v>
+        <v>1381541.378714459</v>
       </c>
       <c r="F20" t="n">
-        <v>1030206.364022448</v>
+        <v>918558.342952241</v>
       </c>
       <c r="G20" t="n">
-        <v>-520832.3377262124</v>
+        <v>-462983.0357622182</v>
       </c>
       <c r="H20" t="n">
-        <v>520832.3377262124</v>
+        <v>462983.0357622182</v>
       </c>
       <c r="I20" t="n">
-        <v>50.77999877929688</v>
+        <v>37.56999969482422</v>
       </c>
       <c r="J20" t="n">
-        <v>10256.64336838379</v>
+        <v>12323.2110599671</v>
       </c>
       <c r="K20" t="n">
-        <v>0.006795315612226852</v>
+        <v>0.01204641157698352</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002471842689459772</v>
+        <v>0.002647608472237999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.002504118344490917</v>
+        <v>0.002547004176653012</v>
       </c>
       <c r="N20" t="n">
-        <v>1509369.682539683</v>
+        <v>1022977.754098361</v>
       </c>
       <c r="O20" t="n">
-        <v>76645790.6368728</v>
+        <v>38433273.90928738</v>
       </c>
       <c r="P20" t="n">
-        <v>210706101.9486</v>
+        <v>174868391.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>4095910</v>
+        <v>4838316</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BEX</t>
+          <t>INTW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1653,57 +1653,57 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01630850587739998</v>
+        <v>0.01466561148621019</v>
       </c>
       <c r="E21" t="n">
-        <v>1528922.426006248</v>
+        <v>1374901.076832205</v>
       </c>
       <c r="F21" t="n">
-        <v>1015344.184149934</v>
+        <v>914760.1541975983</v>
       </c>
       <c r="G21" t="n">
-        <v>-513578.2418563145</v>
+        <v>-460140.9226346068</v>
       </c>
       <c r="H21" t="n">
-        <v>513578.2418563145</v>
+        <v>460140.9226346068</v>
       </c>
       <c r="I21" t="n">
-        <v>54.34999847412109</v>
+        <v>390.0700073242188</v>
       </c>
       <c r="J21" t="n">
-        <v>9449.461936983425</v>
+        <v>1179.636767746018</v>
       </c>
       <c r="K21" t="n">
-        <v>0.009918182654728224</v>
+        <v>0.001554683087008431</v>
       </c>
       <c r="L21" t="n">
-        <v>0.005641027540203672</v>
+        <v>0.0006359888827310753</v>
       </c>
       <c r="M21" t="n">
-        <v>0.005607989280108858</v>
+        <v>0.0005927819974693568</v>
       </c>
       <c r="N21" t="n">
-        <v>952741.2698412698</v>
+        <v>758763.4918032787</v>
       </c>
       <c r="O21" t="n">
-        <v>51781486.56210521</v>
+        <v>295970880.8050547</v>
       </c>
       <c r="P21" t="n">
-        <v>91043384.95</v>
+        <v>723504663.5699999</v>
       </c>
       <c r="Q21" t="n">
-        <v>1685000</v>
+        <v>1990001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BMNU</t>
+          <t>CRDU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1712,57 +1712,57 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01623793126506014</v>
+        <v>0.01463349072455816</v>
       </c>
       <c r="E22" t="n">
-        <v>1522306.056099388</v>
+        <v>1371889.755427328</v>
       </c>
       <c r="F22" t="n">
-        <v>1005218.401174324</v>
+        <v>912756.6378144338</v>
       </c>
       <c r="G22" t="n">
-        <v>-517087.6549250638</v>
+        <v>-459133.1176128942</v>
       </c>
       <c r="H22" t="n">
-        <v>517087.6549250638</v>
+        <v>459133.1176128942</v>
       </c>
       <c r="I22" t="n">
-        <v>2.089999914169312</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="J22" t="n">
-        <v>247410.3713686441</v>
+        <v>6880.459980752989</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001932404434371779</v>
+        <v>0.01361295870487339</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001489870754516291</v>
+        <v>0.006006293569597257</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00146848511021275</v>
+        <v>0.004897187281227083</v>
       </c>
       <c r="N22" t="n">
-        <v>128032396.8253968</v>
+        <v>505434.5737704918</v>
       </c>
       <c r="O22" t="n">
-        <v>267587698.3759706</v>
+        <v>33727650.80441522</v>
       </c>
       <c r="P22" t="n">
-        <v>347068800</v>
+        <v>76442004.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>168480000</v>
+        <v>1404982</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RKLX</t>
+          <t>CRWU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1771,57 +1771,57 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.01569568575612209</v>
+        <v>0.01390252588553467</v>
       </c>
       <c r="E23" t="n">
-        <v>1471470.539636445</v>
+        <v>1303361.801768875</v>
       </c>
       <c r="F23" t="n">
-        <v>979010.5196777957</v>
+        <v>868327.8225402788</v>
       </c>
       <c r="G23" t="n">
-        <v>-492460.0199586497</v>
+        <v>-435033.9792285966</v>
       </c>
       <c r="H23" t="n">
-        <v>492460.0199586497</v>
+        <v>435033.9792285966</v>
       </c>
       <c r="I23" t="n">
-        <v>59.29999923706055</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="J23" t="n">
-        <v>8304.553563145384</v>
+        <v>49211.98775106823</v>
       </c>
       <c r="K23" t="n">
-        <v>0.003159697831084544</v>
+        <v>0.03100972916704495</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001362833872861906</v>
+        <v>0.0159779183767922</v>
       </c>
       <c r="M23" t="n">
-        <v>0.001363637695097764</v>
+        <v>0.02067730577775976</v>
       </c>
       <c r="N23" t="n">
-        <v>2628274.603174603</v>
+        <v>1586985.409836065</v>
       </c>
       <c r="O23" t="n">
-        <v>155856681.9630396</v>
+        <v>14028951.26510558</v>
       </c>
       <c r="P23" t="n">
-        <v>361350000</v>
+        <v>27227200</v>
       </c>
       <c r="Q23" t="n">
-        <v>6090000</v>
+        <v>2380000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LITX</t>
+          <t>RGTX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1830,57 +1830,57 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.01542240887281212</v>
+        <v>0.01350427217007115</v>
       </c>
       <c r="E24" t="n">
-        <v>1445850.831826136</v>
+        <v>1266025.515944171</v>
       </c>
       <c r="F24" t="n">
-        <v>960665.9889314594</v>
+        <v>842038.4041075428</v>
       </c>
       <c r="G24" t="n">
-        <v>-485184.8428946765</v>
+        <v>-423987.1118366278</v>
       </c>
       <c r="H24" t="n">
-        <v>485184.8428946765</v>
+        <v>423987.1118366278</v>
       </c>
       <c r="I24" t="n">
-        <v>44.4900016784668</v>
+        <v>27.67000007629395</v>
       </c>
       <c r="J24" t="n">
-        <v>10905.48043583254</v>
+        <v>15322.98918205914</v>
       </c>
       <c r="K24" t="n">
-        <v>0.002320296963101772</v>
+        <v>0.01470816382253328</v>
       </c>
       <c r="L24" t="n">
-        <v>0.000870227535602004</v>
+        <v>0.006867300159323418</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0008700024280680127</v>
+        <v>0.005904844643500637</v>
       </c>
       <c r="N24" t="n">
-        <v>4700036.507936508</v>
+        <v>1041801.639344262</v>
       </c>
       <c r="O24" t="n">
-        <v>209104632.1269505</v>
+        <v>28826651.4401389</v>
       </c>
       <c r="P24" t="n">
-        <v>557537911.6900001</v>
+        <v>61740000</v>
       </c>
       <c r="Q24" t="n">
-        <v>12535000</v>
+        <v>2594986</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETHU</t>
+          <t>HIMZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ETHA</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1889,57 +1889,57 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.01440261737924271</v>
+        <v>0.01350076442928724</v>
       </c>
       <c r="E25" t="n">
-        <v>1350245.379304004</v>
+        <v>1265696.665245679</v>
       </c>
       <c r="F25" t="n">
-        <v>900313.5634746128</v>
+        <v>842811.0437135443</v>
       </c>
       <c r="G25" t="n">
-        <v>-449931.8158293917</v>
+        <v>-422885.6215321346</v>
       </c>
       <c r="H25" t="n">
-        <v>449931.8158293917</v>
+        <v>422885.6215321346</v>
       </c>
       <c r="I25" t="n">
-        <v>26.51000022888184</v>
+        <v>40.40999984741211</v>
       </c>
       <c r="J25" t="n">
-        <v>16972.15435476325</v>
+        <v>10464.87560328997</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002661291523283028</v>
+        <v>0.004486789191834368</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0004283953595122948</v>
+        <v>0.002631031055385644</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0004283953558136182</v>
+        <v>0.002480059304880757</v>
       </c>
       <c r="N25" t="n">
-        <v>6377412.698412699</v>
+        <v>2332375.147540984</v>
       </c>
       <c r="O25" t="n">
-        <v>169065212.0945946</v>
+        <v>94251279.35623895</v>
       </c>
       <c r="P25" t="n">
-        <v>1050272384.7</v>
+        <v>160730000</v>
       </c>
       <c r="Q25" t="n">
-        <v>39617970</v>
+        <v>4219607</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ONDL</t>
+          <t>WDCX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1948,57 +1948,57 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.01424672666765319</v>
+        <v>0.01344189626326962</v>
       </c>
       <c r="E26" t="n">
-        <v>1335630.625092486</v>
+        <v>1260177.774681527</v>
       </c>
       <c r="F26" t="n">
-        <v>889826.010575635</v>
+        <v>847680.958091829</v>
       </c>
       <c r="G26" t="n">
-        <v>-445804.6145168511</v>
+        <v>-412496.8165896978</v>
       </c>
       <c r="H26" t="n">
-        <v>445804.6145168511</v>
+        <v>412496.8165896978</v>
       </c>
       <c r="I26" t="n">
-        <v>13.90999984741211</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="J26" t="n">
-        <v>32049.21778628136</v>
+        <v>4361.814718418294</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02045848139106403</v>
+        <v>0.007507827167193822</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01023661571795295</v>
+        <v>0.004219330193758981</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01017435485278773</v>
+        <v>0.003665390519679238</v>
       </c>
       <c r="N26" t="n">
-        <v>1566549.206349206</v>
+        <v>580968.9836065574</v>
       </c>
       <c r="O26" t="n">
-        <v>21790699.22128102</v>
+        <v>54942236.60237446</v>
       </c>
       <c r="P26" t="n">
-        <v>43550000</v>
+        <v>97763578.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>3150000</v>
+        <v>1190000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>CRCA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2007,57 +2007,57 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.01423896975835332</v>
+        <v>0.01268043592259913</v>
       </c>
       <c r="E27" t="n">
-        <v>1334903.414845624</v>
+        <v>1188790.867743669</v>
       </c>
       <c r="F27" t="n">
-        <v>887849.3576300765</v>
+        <v>789599.8443240352</v>
       </c>
       <c r="G27" t="n">
-        <v>-447054.0572155471</v>
+        <v>-399191.0234196336</v>
       </c>
       <c r="H27" t="n">
-        <v>447054.0572155471</v>
+        <v>399191.0234196336</v>
       </c>
       <c r="I27" t="n">
-        <v>15.77000045776367</v>
+        <v>67.44000244140625</v>
       </c>
       <c r="J27" t="n">
-        <v>28348.38581095028</v>
+        <v>5919.202386839501</v>
       </c>
       <c r="K27" t="n">
-        <v>0.024724050034147</v>
+        <v>0.003860078709490166</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005549487649342158</v>
+        <v>0.001894539454377135</v>
       </c>
       <c r="M27" t="n">
-        <v>0.005548019089981131</v>
+        <v>0.001445149523998208</v>
       </c>
       <c r="N27" t="n">
-        <v>1146591.507936508</v>
+        <v>1533440.852459016</v>
       </c>
       <c r="O27" t="n">
-        <v>18081748.60502667</v>
+        <v>103415254.8335882</v>
       </c>
       <c r="P27" t="n">
-        <v>80557717.3</v>
+        <v>210706101.9486</v>
       </c>
       <c r="Q27" t="n">
-        <v>5109641</v>
+        <v>4095910</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HIMZ</t>
+          <t>RDTL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2066,57 +2066,57 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.01328539334878896</v>
+        <v>0.01267037504890687</v>
       </c>
       <c r="E28" t="n">
-        <v>1245505.626448965</v>
+        <v>1187847.660835019</v>
       </c>
       <c r="F28" t="n">
-        <v>829366.0920523846</v>
+        <v>789508.4050218002</v>
       </c>
       <c r="G28" t="n">
-        <v>-416139.5343965803</v>
+        <v>-398339.2558132191</v>
       </c>
       <c r="H28" t="n">
-        <v>416139.5343965803</v>
+        <v>398339.2558132191</v>
       </c>
       <c r="I28" t="n">
-        <v>38.13000106811523</v>
+        <v>19.3700008392334</v>
       </c>
       <c r="J28" t="n">
-        <v>10913.70371726953</v>
+        <v>20564.75160323142</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00449176062050162</v>
+        <v>0.03353005301053022</v>
       </c>
       <c r="L28" t="n">
-        <v>0.002589059505982581</v>
+        <v>0.007594433678343371</v>
       </c>
       <c r="M28" t="n">
-        <v>0.002586426583629596</v>
+        <v>0.007245490179531577</v>
       </c>
       <c r="N28" t="n">
-        <v>2429716.238095238</v>
+        <v>613322.9672131147</v>
       </c>
       <c r="O28" t="n">
-        <v>92645082.75378835</v>
+        <v>11880066.38963915</v>
       </c>
       <c r="P28" t="n">
-        <v>160730000</v>
+        <v>52451476</v>
       </c>
       <c r="Q28" t="n">
-        <v>4219607</v>
+        <v>2838283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOLT</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOEZ</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2125,57 +2125,57 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.01317415270324698</v>
+        <v>0.01264499342703624</v>
       </c>
       <c r="E29" t="n">
-        <v>1235076.815929404</v>
+        <v>1185468.133784648</v>
       </c>
       <c r="F29" t="n">
-        <v>825296.8504584673</v>
+        <v>788459.3816799431</v>
       </c>
       <c r="G29" t="n">
-        <v>-409779.9654709371</v>
+        <v>-397008.7521047044</v>
       </c>
       <c r="H29" t="n">
-        <v>409779.9654709371</v>
+        <v>397008.7521047044</v>
       </c>
       <c r="I29" t="n">
-        <v>55.65999984741211</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="J29" t="n">
-        <v>7362.198465582455</v>
+        <v>22493.41420313093</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01040479039449799</v>
+        <v>0.01899914107588317</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002902327317607766</v>
+        <v>0.004928252257027452</v>
       </c>
       <c r="M29" t="n">
-        <v>0.002902327778211074</v>
+        <v>0.004402151580342129</v>
       </c>
       <c r="N29" t="n">
-        <v>707577.7777777778</v>
+        <v>1183917.426229508</v>
       </c>
       <c r="O29" t="n">
-        <v>39383779.00314331</v>
+        <v>20896142.12132216</v>
       </c>
       <c r="P29" t="n">
-        <v>141190128</v>
+        <v>80557717.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>2536653</v>
+        <v>5109641</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IONX</t>
+          <t>RKLX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2184,57 +2184,57 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.01305281640650354</v>
+        <v>0.0119760120335414</v>
       </c>
       <c r="E30" t="n">
-        <v>1223701.538109707</v>
+        <v>1122751.128144506</v>
       </c>
       <c r="F30" t="n">
-        <v>813751.2740863545</v>
+        <v>746746.0617866673</v>
       </c>
       <c r="G30" t="n">
-        <v>-409950.2640233524</v>
+        <v>-376005.0663578385</v>
       </c>
       <c r="H30" t="n">
-        <v>409950.2640233524</v>
+        <v>376005.0663578385</v>
       </c>
       <c r="I30" t="n">
-        <v>52.63999938964844</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="J30" t="n">
-        <v>7787.809057307254</v>
+        <v>5181.274189596775</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003716378580452986</v>
+        <v>0.00189483097747683</v>
       </c>
       <c r="L30" t="n">
-        <v>0.001212225039988623</v>
+        <v>0.001040556431044247</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001213688059140419</v>
+        <v>0.0008507839391784524</v>
       </c>
       <c r="N30" t="n">
-        <v>2095537.063492063</v>
+        <v>2734425.524590164</v>
       </c>
       <c r="O30" t="n">
-        <v>110309069.7432079</v>
+        <v>198437259.4850278</v>
       </c>
       <c r="P30" t="n">
-        <v>338180000</v>
+        <v>361350000</v>
       </c>
       <c r="Q30" t="n">
-        <v>6416648</v>
+        <v>6090000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCUP</t>
+          <t>KORU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2243,57 +2243,57 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.01283254877582277</v>
+        <v>0.01192796419756183</v>
       </c>
       <c r="E31" t="n">
-        <v>1203051.447733385</v>
+        <v>1118246.643521422</v>
       </c>
       <c r="F31" t="n">
-        <v>800962.0601219594</v>
+        <v>833777.8967594218</v>
       </c>
       <c r="G31" t="n">
-        <v>-402089.3876114254</v>
+        <v>-284468.7467619999</v>
       </c>
       <c r="H31" t="n">
-        <v>402089.3876114254</v>
+        <v>284468.7467619999</v>
       </c>
       <c r="I31" t="n">
-        <v>5.760000228881836</v>
+        <v>983.0900268554688</v>
       </c>
       <c r="J31" t="n">
-        <v>69807.18257531759</v>
+        <v>289.3618478379923</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02121414025460238</v>
+        <v>0.0002768004570508173</v>
       </c>
       <c r="L31" t="n">
-        <v>0.008945258901255294</v>
+        <v>0.0001555980354090482</v>
       </c>
       <c r="M31" t="n">
-        <v>0.009007378396815173</v>
+        <v>0.0001215844908652513</v>
       </c>
       <c r="N31" t="n">
-        <v>3290596.825396826</v>
+        <v>1045380.672131148</v>
       </c>
       <c r="O31" t="n">
-        <v>18953838.46744356</v>
+        <v>1027703313.039598</v>
       </c>
       <c r="P31" t="n">
-        <v>44950000</v>
+        <v>1828228396.420086</v>
       </c>
       <c r="Q31" t="n">
-        <v>7750000</v>
+        <v>2379924</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XXRP</t>
+          <t>SOXL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>XRPZ</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2302,57 +2302,57 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.01244087462810518</v>
+        <v>0.01175564917643995</v>
       </c>
       <c r="E32" t="n">
-        <v>1166331.99638486</v>
+        <v>1102092.110291246</v>
       </c>
       <c r="F32" t="n">
-        <v>780129.3485753039</v>
+        <v>823786.0218338604</v>
       </c>
       <c r="G32" t="n">
-        <v>-386202.6478095564</v>
+        <v>-278306.0884573853</v>
       </c>
       <c r="H32" t="n">
-        <v>386202.6478095564</v>
+        <v>278306.0884573853</v>
       </c>
       <c r="I32" t="n">
-        <v>4.150000095367432</v>
+        <v>190.4199981689453</v>
       </c>
       <c r="J32" t="n">
-        <v>93060.87685170592</v>
+        <v>1461.538132200092</v>
       </c>
       <c r="K32" t="n">
-        <v>0.03886507375925564</v>
+        <v>1.768017204899147e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>0.003173248516944212</v>
+        <v>1.446523884502442e-05</v>
       </c>
       <c r="M32" t="n">
-        <v>0.003173248561351654</v>
+        <v>1.154452953813839e-05</v>
       </c>
       <c r="N32" t="n">
-        <v>2394460.317460318</v>
+        <v>82665379.50819673</v>
       </c>
       <c r="O32" t="n">
-        <v>9937010.545813849</v>
+        <v>15741141414.58599</v>
       </c>
       <c r="P32" t="n">
-        <v>121705768</v>
+        <v>19239646952.19074</v>
       </c>
       <c r="Q32" t="n">
-        <v>29326690</v>
+        <v>126600060</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APPX</t>
+          <t>BMNU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2361,57 +2361,57 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.01215831240419335</v>
+        <v>0.01164791251393471</v>
       </c>
       <c r="E33" t="n">
-        <v>1139841.787893127</v>
+        <v>1091991.798181379</v>
       </c>
       <c r="F33" t="n">
-        <v>757857.2745241165</v>
+        <v>721070.6710817256</v>
       </c>
       <c r="G33" t="n">
-        <v>-381984.5133690104</v>
+        <v>-370921.1270996531</v>
       </c>
       <c r="H33" t="n">
-        <v>381984.5133690104</v>
+        <v>370921.1270996531</v>
       </c>
       <c r="I33" t="n">
-        <v>36.11000061035156</v>
+        <v>2.25</v>
       </c>
       <c r="J33" t="n">
-        <v>10578.35798705325</v>
+        <v>164853.8342665125</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01001596399356776</v>
+        <v>0.001255597551214348</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002184411427072059</v>
+        <v>0.001068725068630926</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002186371867206122</v>
+        <v>0.0009784771739465366</v>
       </c>
       <c r="N33" t="n">
-        <v>1056149.761904762</v>
+        <v>131295122.4754098</v>
       </c>
       <c r="O33" t="n">
-        <v>38137568.54700361</v>
+        <v>295414025.5696721</v>
       </c>
       <c r="P33" t="n">
-        <v>174868391.84</v>
+        <v>347068800</v>
       </c>
       <c r="Q33" t="n">
-        <v>4838316</v>
+        <v>168480000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UXRP</t>
+          <t>UPSX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XRPZ</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2420,57 +2420,57 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.01212317350438085</v>
+        <v>0.01161266875072488</v>
       </c>
       <c r="E34" t="n">
-        <v>1136547.516035704</v>
+        <v>1088687.695380458</v>
       </c>
       <c r="F34" t="n">
-        <v>757572.018858077</v>
+        <v>724456.2817369456</v>
       </c>
       <c r="G34" t="n">
-        <v>-378975.4971776273</v>
+        <v>-364231.4136435121</v>
       </c>
       <c r="H34" t="n">
-        <v>378975.4971776273</v>
+        <v>364231.4136435121</v>
       </c>
       <c r="I34" t="n">
-        <v>3.990000009536743</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="J34" t="n">
-        <v>94981.32738641974</v>
+        <v>22249.93249667842</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2053678514795379</v>
+        <v>0.2466014648957064</v>
       </c>
       <c r="L34" t="n">
-        <v>0.008779121809723801</v>
+        <v>0.01461083769237058</v>
       </c>
       <c r="M34" t="n">
-        <v>0.008754039390453432</v>
+        <v>0.01492299543098641</v>
       </c>
       <c r="N34" t="n">
-        <v>462493.6507936508</v>
+        <v>90226.27868852459</v>
       </c>
       <c r="O34" t="n">
-        <v>1845349.67107735</v>
+        <v>1477004.257852054</v>
       </c>
       <c r="P34" t="n">
-        <v>43167813.9786</v>
+        <v>24928852.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>10850000</v>
+        <v>1490983</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WDCX</t>
+          <t>TEMT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2479,57 +2479,57 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.01069918252153211</v>
+        <v>0.01157586631745447</v>
       </c>
       <c r="E35" t="n">
-        <v>1003048.361393635</v>
+        <v>1085237.467261357</v>
       </c>
       <c r="F35" t="n">
-        <v>674718.2921976825</v>
+        <v>721673.8266377865</v>
       </c>
       <c r="G35" t="n">
-        <v>-328330.0691959526</v>
+        <v>-363563.64062357</v>
       </c>
       <c r="H35" t="n">
-        <v>328330.0691959526</v>
+        <v>363563.64062357</v>
       </c>
       <c r="I35" t="n">
-        <v>82.29000091552734</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="J35" t="n">
-        <v>3989.914516260502</v>
+        <v>19338.49230732281</v>
       </c>
       <c r="K35" t="n">
-        <v>0.006967119506091174</v>
+        <v>0.06719758902558641</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003358408886474924</v>
+        <v>0.007384542826158004</v>
       </c>
       <c r="M35" t="n">
-        <v>0.00335286934139538</v>
+        <v>0.007850587016098939</v>
       </c>
       <c r="N35" t="n">
-        <v>572677.7777777778</v>
+        <v>287785.5081967213</v>
       </c>
       <c r="O35" t="n">
-        <v>47125654.8576355</v>
+        <v>5410367.334535442</v>
       </c>
       <c r="P35" t="n">
-        <v>97763578.02</v>
+        <v>49233060.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>1190000</v>
+        <v>2463318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETHT</t>
+          <t>SOLT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ETHA</t>
+          <t>SOEZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2538,57 +2538,57 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.01067345392042911</v>
+        <v>0.01081031619369076</v>
       </c>
       <c r="E36" t="n">
-        <v>1000636.305040229</v>
+        <v>1013467.143158509</v>
       </c>
       <c r="F36" t="n">
-        <v>666087.2227800385</v>
+        <v>677213.9437031312</v>
       </c>
       <c r="G36" t="n">
-        <v>-334549.0822601901</v>
+        <v>-336253.199455378</v>
       </c>
       <c r="H36" t="n">
-        <v>334549.0822601901</v>
+        <v>336253.199455378</v>
       </c>
       <c r="I36" t="n">
-        <v>17.61000061035156</v>
+        <v>62.40000152587891</v>
       </c>
       <c r="J36" t="n">
-        <v>18997.675790172</v>
+        <v>5388.67293642493</v>
       </c>
       <c r="K36" t="n">
-        <v>0.009003935846675406</v>
+        <v>0.007949449017548687</v>
       </c>
       <c r="L36" t="n">
-        <v>0.001269517526913785</v>
+        <v>0.002381563103727606</v>
       </c>
       <c r="M36" t="n">
-        <v>0.001269906602996812</v>
+        <v>0.002124324035027625</v>
       </c>
       <c r="N36" t="n">
-        <v>2109930.158730159</v>
+        <v>677867.475409836</v>
       </c>
       <c r="O36" t="n">
-        <v>37155871.38303726</v>
+        <v>42298931.49991745</v>
       </c>
       <c r="P36" t="n">
-        <v>263524587.2292</v>
+        <v>141190128</v>
       </c>
       <c r="Q36" t="n">
-        <v>14959900</v>
+        <v>2536653</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTW</t>
+          <t>JNUG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>GDXJ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2597,57 +2597,57 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.01013069600226033</v>
+        <v>0.01076894587559617</v>
       </c>
       <c r="E37" t="n">
-        <v>949752.7502119062</v>
+        <v>1009588.675837141</v>
       </c>
       <c r="F37" t="n">
-        <v>631897.0774502241</v>
+        <v>670117.0296242489</v>
       </c>
       <c r="G37" t="n">
-        <v>-317855.6727616821</v>
+        <v>-339471.646212892</v>
       </c>
       <c r="H37" t="n">
-        <v>317855.6727616821</v>
+        <v>339471.646212892</v>
       </c>
       <c r="I37" t="n">
-        <v>363.5700073242188</v>
+        <v>223.8899993896484</v>
       </c>
       <c r="J37" t="n">
-        <v>874.2626354165398</v>
+        <v>1516.243008344872</v>
       </c>
       <c r="K37" t="n">
-        <v>0.001153603031769784</v>
+        <v>0.005624248541596336</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0004393277455784211</v>
+        <v>0.0006504687971723924</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0004393277367280417</v>
+        <v>0.0005846655575527075</v>
       </c>
       <c r="N37" t="n">
-        <v>757853.9682539683</v>
+        <v>269590.3278688525</v>
       </c>
       <c r="O37" t="n">
-        <v>275532972.7887835</v>
+        <v>60358578.3420125</v>
       </c>
       <c r="P37" t="n">
-        <v>723504663.5699999</v>
+        <v>521887671.9199838</v>
       </c>
       <c r="Q37" t="n">
-        <v>1990001</v>
+        <v>2593351</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IONL</t>
+          <t>COHX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2656,57 +2656,57 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.009617072817398474</v>
+        <v>0.01027572030035611</v>
       </c>
       <c r="E38" t="n">
-        <v>901600.5766311069</v>
+        <v>963348.7781583855</v>
       </c>
       <c r="F38" t="n">
-        <v>599556.8323660794</v>
+        <v>642446.4536552591</v>
       </c>
       <c r="G38" t="n">
-        <v>-302043.7442650274</v>
+        <v>-320902.3245031265</v>
       </c>
       <c r="H38" t="n">
-        <v>302043.7442650274</v>
+        <v>320902.3245031265</v>
       </c>
       <c r="I38" t="n">
-        <v>27.65999984741211</v>
+        <v>59.72000122070312</v>
       </c>
       <c r="J38" t="n">
-        <v>10919.87512405163</v>
+        <v>5373.448056660108</v>
       </c>
       <c r="K38" t="n">
-        <v>0.01171345221524375</v>
+        <v>0.008603672410723668</v>
       </c>
       <c r="L38" t="n">
-        <v>0.002951316787160746</v>
+        <v>0.002695438790260771</v>
       </c>
       <c r="M38" t="n">
-        <v>0.002951316803441845</v>
+        <v>0.002128098240261429</v>
       </c>
       <c r="N38" t="n">
-        <v>932250.7936507936</v>
+        <v>624552.8421052631</v>
       </c>
       <c r="O38" t="n">
-        <v>25786056.81013077</v>
+        <v>37298296.49291992</v>
       </c>
       <c r="P38" t="n">
-        <v>102342027.66</v>
+        <v>119053834.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>3700001</v>
+        <v>2525000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CONL</t>
+          <t>ONDL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2715,57 +2715,57 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.009005891361791984</v>
+        <v>0.01008360876935725</v>
       </c>
       <c r="E39" t="n">
-        <v>844302.3151679984</v>
+        <v>945338.322127242</v>
       </c>
       <c r="F39" t="n">
-        <v>561643.3546162748</v>
+        <v>629699.4833535386</v>
       </c>
       <c r="G39" t="n">
-        <v>-282658.9605517236</v>
+        <v>-315638.8387737035</v>
       </c>
       <c r="H39" t="n">
-        <v>282658.9605517236</v>
+        <v>315638.8387737035</v>
       </c>
       <c r="I39" t="n">
-        <v>8.819999694824219</v>
+        <v>14.97000026702881</v>
       </c>
       <c r="J39" t="n">
-        <v>32047.50230519786</v>
+        <v>21084.75839301707</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00158182556907535</v>
+        <v>0.01334608918402967</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0004271291585927147</v>
+        <v>0.007247734529820976</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0004271291733715673</v>
+        <v>0.006693574093021293</v>
       </c>
       <c r="N39" t="n">
-        <v>20259820.63492063</v>
+        <v>1579845.459016393</v>
       </c>
       <c r="O39" t="n">
-        <v>178691611.8171934</v>
+        <v>23650286.94333966</v>
       </c>
       <c r="P39" t="n">
-        <v>661764608.8200001</v>
+        <v>43550000</v>
       </c>
       <c r="Q39" t="n">
-        <v>75030001</v>
+        <v>3150000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>XRPT</t>
+          <t>BABX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XRPZ</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2774,57 +2774,57 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.00897655970538468</v>
+        <v>0.01000177295127002</v>
       </c>
       <c r="E40" t="n">
-        <v>841552.4723798138</v>
+        <v>937666.214181564</v>
       </c>
       <c r="F40" t="n">
-        <v>562708.0481320291</v>
+        <v>625734.6725376638</v>
       </c>
       <c r="G40" t="n">
-        <v>-278844.4242477845</v>
+        <v>-311931.5416439003</v>
       </c>
       <c r="H40" t="n">
-        <v>278844.4242477845</v>
+        <v>311931.5416439003</v>
       </c>
       <c r="I40" t="n">
-        <v>43.72000122070312</v>
+        <v>28.8700008392334</v>
       </c>
       <c r="J40" t="n">
-        <v>6377.960120361132</v>
+        <v>10804.6945817887</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03401342616493511</v>
+        <v>0.01628855648497175</v>
       </c>
       <c r="L40" t="n">
-        <v>0.00393504174216262</v>
+        <v>0.00263169159642586</v>
       </c>
       <c r="M40" t="n">
-        <v>0.003935042469702594</v>
+        <v>0.002739256154129966</v>
       </c>
       <c r="N40" t="n">
-        <v>187513.0158730159</v>
+        <v>663330.393442623</v>
       </c>
       <c r="O40" t="n">
-        <v>8198069.282865979</v>
+        <v>19150349.01537754</v>
       </c>
       <c r="P40" t="n">
-        <v>70861872</v>
+        <v>118528912</v>
       </c>
       <c r="Q40" t="n">
-        <v>1620811</v>
+        <v>3944390</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MUU</t>
+          <t>CONL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2833,57 +2833,57 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.008824176316994316</v>
+        <v>0.009937846807592351</v>
       </c>
       <c r="E41" t="n">
-        <v>827266.5297182171</v>
+        <v>931673.1382117829</v>
       </c>
       <c r="F41" t="n">
-        <v>550958.4035598279</v>
+        <v>619763.8184220999</v>
       </c>
       <c r="G41" t="n">
-        <v>-276308.1261583891</v>
+        <v>-311909.3197896829</v>
       </c>
       <c r="H41" t="n">
-        <v>276308.1261583891</v>
+        <v>311909.3197896829</v>
       </c>
       <c r="I41" t="n">
-        <v>542.719970703125</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="J41" t="n">
-        <v>509.1173000330466</v>
+        <v>30760.2869062107</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0001988639577382456</v>
+        <v>0.001483332953835801</v>
       </c>
       <c r="L41" t="n">
-        <v>9.697470010959958e-05</v>
+        <v>0.0004713297079241695</v>
       </c>
       <c r="M41" t="n">
-        <v>9.697470534444596e-05</v>
+        <v>0.0004099731640175602</v>
       </c>
       <c r="N41" t="n">
-        <v>2560128.571428571</v>
+        <v>20737277.37704918</v>
       </c>
       <c r="O41" t="n">
-        <v>1389432903.281948</v>
+        <v>210275999.7228579</v>
       </c>
       <c r="P41" t="n">
-        <v>2849280542.72</v>
+        <v>661764608.8200001</v>
       </c>
       <c r="Q41" t="n">
-        <v>5250001</v>
+        <v>75030001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QPUX</t>
+          <t>ETHU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>ETHA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2892,57 +2892,57 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.008614331400614168</v>
+        <v>0.00988562860563006</v>
       </c>
       <c r="E42" t="n">
-        <v>807593.5688075782</v>
+        <v>926777.6817778181</v>
       </c>
       <c r="F42" t="n">
-        <v>534757.9036698829</v>
+        <v>617954.7288361926</v>
       </c>
       <c r="G42" t="n">
-        <v>-272835.6651376954</v>
+        <v>-308822.9529416255</v>
       </c>
       <c r="H42" t="n">
-        <v>272835.6651376954</v>
+        <v>308822.9529416255</v>
       </c>
       <c r="I42" t="n">
-        <v>30.60899925231934</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="J42" t="n">
-        <v>8913.576784677853</v>
+        <v>11429.42071464293</v>
       </c>
       <c r="K42" t="n">
-        <v>0.07076616355198591</v>
+        <v>0.001828198396657259</v>
       </c>
       <c r="L42" t="n">
-        <v>0.007570356968304533</v>
+        <v>0.0002940408197344327</v>
       </c>
       <c r="M42" t="n">
-        <v>0.007532697706514946</v>
+        <v>0.000288490821580281</v>
       </c>
       <c r="N42" t="n">
-        <v>125958.1746031746</v>
+        <v>6251739.819672131</v>
       </c>
       <c r="O42" t="n">
-        <v>3855453.67225208</v>
+        <v>168922012.7893603</v>
       </c>
       <c r="P42" t="n">
-        <v>36040000</v>
+        <v>1050272384.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>1183318</v>
+        <v>39617970</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RDTL</t>
+          <t>CCUP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2951,57 +2951,57 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.008484384118408503</v>
+        <v>0.009835013897030833</v>
       </c>
       <c r="E43" t="n">
-        <v>795411.0111007971</v>
+        <v>922032.5528466407</v>
       </c>
       <c r="F43" t="n">
-        <v>528673.5828309121</v>
+        <v>613763.5615906591</v>
       </c>
       <c r="G43" t="n">
-        <v>-266737.428269885</v>
+        <v>-308268.9912559815</v>
       </c>
       <c r="H43" t="n">
-        <v>266737.428269885</v>
+        <v>308268.9912559815</v>
       </c>
       <c r="I43" t="n">
-        <v>18.47999954223633</v>
+        <v>7.650000095367432</v>
       </c>
       <c r="J43" t="n">
-        <v>14433.84387863498</v>
+        <v>40296.59966182984</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02302864650021535</v>
+        <v>0.01137777825748853</v>
       </c>
       <c r="L43" t="n">
-        <v>0.005085413197330901</v>
+        <v>0.006858042074660322</v>
       </c>
       <c r="M43" t="n">
-        <v>0.005085413920541038</v>
+        <v>0.005199561246687721</v>
       </c>
       <c r="N43" t="n">
-        <v>626777.7777777778</v>
+        <v>3541693.180327869</v>
       </c>
       <c r="O43" t="n">
-        <v>11582853.04641724</v>
+        <v>27093953.16727038</v>
       </c>
       <c r="P43" t="n">
-        <v>52451476</v>
+        <v>44950000</v>
       </c>
       <c r="Q43" t="n">
-        <v>2838283</v>
+        <v>7750000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RIOX</t>
+          <t>IONX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3010,57 +3010,57 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.008410406142038605</v>
+        <v>0.009803311166279551</v>
       </c>
       <c r="E44" t="n">
-        <v>788475.5758161193</v>
+        <v>919060.421838708</v>
       </c>
       <c r="F44" t="n">
-        <v>525211.6106020561</v>
+        <v>610961.0514603278</v>
       </c>
       <c r="G44" t="n">
-        <v>-263263.9652140632</v>
+        <v>-308099.3703783801</v>
       </c>
       <c r="H44" t="n">
-        <v>263263.9652140632</v>
+        <v>308099.3703783801</v>
       </c>
       <c r="I44" t="n">
-        <v>50.45000076293945</v>
+        <v>69.01999664306641</v>
       </c>
       <c r="J44" t="n">
-        <v>5218.314395100204</v>
+        <v>4463.914595239713</v>
       </c>
       <c r="K44" t="n">
-        <v>0.02161815894402503</v>
+        <v>0.002046396150052822</v>
       </c>
       <c r="L44" t="n">
-        <v>0.00819116257666656</v>
+        <v>0.0009110514234383467</v>
       </c>
       <c r="M44" t="n">
-        <v>0.008175152660133106</v>
+        <v>0.0006956770256432507</v>
       </c>
       <c r="N44" t="n">
-        <v>241385.6984126984</v>
+        <v>2181354.081967213</v>
       </c>
       <c r="O44" t="n">
-        <v>12177908.66908331</v>
+        <v>150557051.4147162</v>
       </c>
       <c r="P44" t="n">
-        <v>32140000</v>
+        <v>338180000</v>
       </c>
       <c r="Q44" t="n">
-        <v>638314</v>
+        <v>6416648</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TEMT</t>
+          <t>GEVX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3069,57 +3069,57 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.008075298441991259</v>
+        <v>0.009793771520020205</v>
       </c>
       <c r="E45" t="n">
-        <v>757059.2289366806</v>
+        <v>918166.0800018943</v>
       </c>
       <c r="F45" t="n">
-        <v>503438.046713337</v>
+        <v>611394.9206293938</v>
       </c>
       <c r="G45" t="n">
-        <v>-253621.1822233436</v>
+        <v>-306771.1593725006</v>
       </c>
       <c r="H45" t="n">
-        <v>253621.1822233436</v>
+        <v>306771.1593725006</v>
       </c>
       <c r="I45" t="n">
-        <v>19.8799991607666</v>
+        <v>75.33999633789062</v>
       </c>
       <c r="J45" t="n">
-        <v>12757.6052781666</v>
+        <v>4071.823391079947</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0455634829899659</v>
+        <v>0.04664778706866115</v>
       </c>
       <c r="L45" t="n">
-        <v>0.005151440552572364</v>
+        <v>0.00792752513951964</v>
       </c>
       <c r="M45" t="n">
-        <v>0.005179033027066177</v>
+        <v>0.007471235579963206</v>
       </c>
       <c r="N45" t="n">
-        <v>279996.2698412698</v>
+        <v>87288.67213114754</v>
       </c>
       <c r="O45" t="n">
-        <v>5566325.609462223</v>
+        <v>6576328.238699991</v>
       </c>
       <c r="P45" t="n">
-        <v>49233060.08</v>
+        <v>38696964.56</v>
       </c>
       <c r="Q45" t="n">
-        <v>2463318</v>
+        <v>545000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMDL</t>
+          <t>XXRP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XRPZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3128,57 +3128,57 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.007937797614157147</v>
+        <v>0.009489810830072417</v>
       </c>
       <c r="E46" t="n">
-        <v>744168.5263272325</v>
+        <v>889669.7653192891</v>
       </c>
       <c r="F46" t="n">
-        <v>495864.0464048993</v>
+        <v>595077.1277963456</v>
       </c>
       <c r="G46" t="n">
-        <v>-248304.4799223332</v>
+        <v>-294592.6375229434</v>
       </c>
       <c r="H46" t="n">
-        <v>248304.4799223332</v>
+        <v>294592.6375229434</v>
       </c>
       <c r="I46" t="n">
-        <v>55.7400016784668</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
-        <v>4454.690930127061</v>
+        <v>65465.03056065409</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0003638834727081813</v>
+        <v>0.02704202422045219</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0001669674311944762</v>
+        <v>0.002420531437120904</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0001669674261666814</v>
+        <v>0.002232267963437199</v>
       </c>
       <c r="N46" t="n">
-        <v>12242080.95238095</v>
+        <v>2420862.803278688</v>
       </c>
       <c r="O46" t="n">
-        <v>682373612.8336407</v>
+        <v>10893882.6147541</v>
       </c>
       <c r="P46" t="n">
-        <v>1487143200</v>
+        <v>121705768</v>
       </c>
       <c r="Q46" t="n">
-        <v>26680000</v>
+        <v>29326690</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UPSX</t>
+          <t>GDXU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3187,57 +3187,57 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.007883100604104278</v>
+        <v>0.009234731844532346</v>
       </c>
       <c r="E47" t="n">
-        <v>739040.6816347761</v>
+        <v>865756.1104249075</v>
       </c>
       <c r="F47" t="n">
-        <v>491787.191626487</v>
+        <v>651619.0561521132</v>
       </c>
       <c r="G47" t="n">
-        <v>-247253.4900082891</v>
+        <v>-214137.0542727943</v>
       </c>
       <c r="H47" t="n">
-        <v>247253.4900082891</v>
+        <v>214137.0542727943</v>
       </c>
       <c r="I47" t="n">
-        <v>16.79000091552734</v>
+        <v>223.0500030517578</v>
       </c>
       <c r="J47" t="n">
-        <v>14726.23445658242</v>
+        <v>960.040579883358</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1507560563478538</v>
+        <v>0.0008231467194039955</v>
       </c>
       <c r="L47" t="n">
-        <v>0.009918366390327501</v>
+        <v>0.0001486691270152035</v>
       </c>
       <c r="M47" t="n">
-        <v>0.009876862752011537</v>
+        <v>0.0001359650975187359</v>
       </c>
       <c r="N47" t="n">
-        <v>97682.53968253969</v>
+        <v>1166305.540983607</v>
       </c>
       <c r="O47" t="n">
-        <v>1640089.930700877</v>
+        <v>260144454.4756755</v>
       </c>
       <c r="P47" t="n">
-        <v>24928852.22</v>
+        <v>1440359936</v>
       </c>
       <c r="Q47" t="n">
-        <v>1490983</v>
+        <v>7060934</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMUU</t>
+          <t>UXRP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XRPZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3246,57 +3246,57 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.007728473483452841</v>
+        <v>0.009230792777923011</v>
       </c>
       <c r="E48" t="n">
-        <v>724544.3890737038</v>
+        <v>865386.8229302822</v>
       </c>
       <c r="F48" t="n">
-        <v>483671.9193018608</v>
+        <v>576828.3624667003</v>
       </c>
       <c r="G48" t="n">
-        <v>-240872.469771843</v>
+        <v>-288558.4604635819</v>
       </c>
       <c r="H48" t="n">
-        <v>240872.469771843</v>
+        <v>288558.4604635819</v>
       </c>
       <c r="I48" t="n">
-        <v>194.9299926757812</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="J48" t="n">
-        <v>1235.68706111058</v>
+        <v>66641.67795564397</v>
       </c>
       <c r="K48" t="n">
-        <v>0.007946702821469998</v>
+        <v>0.1428598161426671</v>
       </c>
       <c r="L48" t="n">
-        <v>0.001977096060136525</v>
+        <v>0.006684574312857996</v>
       </c>
       <c r="M48" t="n">
-        <v>0.001977096134423113</v>
+        <v>0.006142090134160735</v>
       </c>
       <c r="N48" t="n">
-        <v>155496.8253968254</v>
+        <v>466483.0163934426</v>
       </c>
       <c r="O48" t="n">
-        <v>30310995.03571041</v>
+        <v>2019871.425393777</v>
       </c>
       <c r="P48" t="n">
-        <v>121831444.93</v>
+        <v>43167813.9786</v>
       </c>
       <c r="Q48" t="n">
-        <v>625001</v>
+        <v>10850000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMDG</t>
+          <t>URAA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3305,57 +3305,57 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.007585359280375199</v>
+        <v>0.009098979687705766</v>
       </c>
       <c r="E49" t="n">
-        <v>711127.4325351749</v>
+        <v>853029.3457224156</v>
       </c>
       <c r="F49" t="n">
-        <v>474321.7606952898</v>
+        <v>562190.8371228876</v>
       </c>
       <c r="G49" t="n">
-        <v>-236805.6718398851</v>
+        <v>-290838.508599528</v>
       </c>
       <c r="H49" t="n">
-        <v>236805.6718398851</v>
+        <v>290838.508599528</v>
       </c>
       <c r="I49" t="n">
-        <v>94.29000091552734</v>
+        <v>43.90999984741211</v>
       </c>
       <c r="J49" t="n">
-        <v>2511.46112568219</v>
+        <v>6623.51422478242</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02233323700956695</v>
+        <v>0.08140840021150836</v>
       </c>
       <c r="L49" t="n">
-        <v>0.009198176405762126</v>
+        <v>0.005305309477478112</v>
       </c>
       <c r="M49" t="n">
-        <v>0.009198177277539804</v>
+        <v>0.005298807140780223</v>
       </c>
       <c r="N49" t="n">
-        <v>112453.9682539683</v>
+        <v>81361.55737704918</v>
       </c>
       <c r="O49" t="n">
-        <v>10603284.76962135</v>
+        <v>3572585.972011441</v>
       </c>
       <c r="P49" t="n">
-        <v>25744850</v>
+        <v>54820272</v>
       </c>
       <c r="Q49" t="n">
-        <v>273039</v>
+        <v>1250001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IREX</t>
+          <t>NVOX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3364,57 +3364,57 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.007493148124672415</v>
+        <v>0.009020887400540642</v>
       </c>
       <c r="E50" t="n">
-        <v>702482.6366880389</v>
+        <v>845708.1938006852</v>
       </c>
       <c r="F50" t="n">
-        <v>467852.4975136773</v>
+        <v>564368.1426361193</v>
       </c>
       <c r="G50" t="n">
-        <v>-234630.1391743617</v>
+        <v>-281340.051164566</v>
       </c>
       <c r="H50" t="n">
-        <v>234630.1391743617</v>
+        <v>281340.051164566</v>
       </c>
       <c r="I50" t="n">
-        <v>49.65999984741211</v>
+        <v>15.6899995803833</v>
       </c>
       <c r="J50" t="n">
-        <v>4724.730968491713</v>
+        <v>17931.17008851398</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00469509959872106</v>
+        <v>0.01613528484671119</v>
       </c>
       <c r="L50" t="n">
-        <v>0.002902766116347588</v>
+        <v>0.005369084945888663</v>
       </c>
       <c r="M50" t="n">
-        <v>0.002907560745935929</v>
+        <v>0.005292395382697854</v>
       </c>
       <c r="N50" t="n">
-        <v>1006311.126984127</v>
+        <v>1111301.737704918</v>
       </c>
       <c r="O50" t="n">
-        <v>49973410.41248085</v>
+        <v>17436323.7982694</v>
       </c>
       <c r="P50" t="n">
-        <v>80829846.34999999</v>
+        <v>52400000</v>
       </c>
       <c r="Q50" t="n">
-        <v>1624981</v>
+        <v>3388101</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ROBN</t>
+          <t>SMCL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3423,57 +3423,57 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.00744005562156632</v>
+        <v>0.00897647212870996</v>
       </c>
       <c r="E51" t="n">
-        <v>697505.2145218425</v>
+        <v>841544.2620665588</v>
       </c>
       <c r="F51" t="n">
-        <v>465929.778093608</v>
+        <v>560091.3316095157</v>
       </c>
       <c r="G51" t="n">
-        <v>-231575.4364282346</v>
+        <v>-281452.9304570431</v>
       </c>
       <c r="H51" t="n">
-        <v>231575.4364282346</v>
+        <v>281452.9304570431</v>
       </c>
       <c r="I51" t="n">
-        <v>19.63999938964844</v>
+        <v>66.06109619140625</v>
       </c>
       <c r="J51" t="n">
-        <v>11791.01036786641</v>
+        <v>4260.494401145839</v>
       </c>
       <c r="K51" t="n">
-        <v>0.007441873299287239</v>
+        <v>0.005646852023036816</v>
       </c>
       <c r="L51" t="n">
-        <v>0.001470712421269384</v>
+        <v>0.01002122542366939</v>
       </c>
       <c r="M51" t="n">
-        <v>0.001446749738388516</v>
+        <v>0.01121793819566406</v>
       </c>
       <c r="N51" t="n">
-        <v>1584414.285714286</v>
+        <v>754490.1803278689</v>
       </c>
       <c r="O51" t="n">
-        <v>31117895.60437883</v>
+        <v>49842448.3781108</v>
       </c>
       <c r="P51" t="n">
-        <v>157458000</v>
+        <v>28085680</v>
       </c>
       <c r="Q51" t="n">
-        <v>8150000</v>
+        <v>379793</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LUNL</t>
+          <t>LRCU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3482,57 +3482,57 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.007313228376530873</v>
+        <v>0.008917338363838059</v>
       </c>
       <c r="E52" t="n">
-        <v>685615.1602997694</v>
+        <v>836000.4716098181</v>
       </c>
       <c r="F52" t="n">
-        <v>456465.7083279213</v>
+        <v>561451.8766640649</v>
       </c>
       <c r="G52" t="n">
-        <v>-229149.4519718481</v>
+        <v>-274548.5949457531</v>
       </c>
       <c r="H52" t="n">
-        <v>229149.4519718481</v>
+        <v>274548.5949457531</v>
       </c>
       <c r="I52" t="n">
-        <v>24.25</v>
+        <v>56.97000122070312</v>
       </c>
       <c r="J52" t="n">
-        <v>9449.461936983425</v>
+        <v>4819.178323029086</v>
       </c>
       <c r="K52" t="n">
-        <v>0.01724294434297139</v>
+        <v>0.04415144803124053</v>
       </c>
       <c r="L52" t="n">
-        <v>0.00722185477377397</v>
+        <v>0.009184813315159863</v>
       </c>
       <c r="M52" t="n">
-        <v>0.007213329722888111</v>
+        <v>0.009092789288734124</v>
       </c>
       <c r="N52" t="n">
-        <v>548019.0476190476</v>
+        <v>109151.0819672131</v>
       </c>
       <c r="O52" t="n">
-        <v>13289461.9047619</v>
+        <v>6218337.272913198</v>
       </c>
       <c r="P52" t="n">
-        <v>31730000</v>
+        <v>29891581.41</v>
       </c>
       <c r="Q52" t="n">
-        <v>1310000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JNUG</t>
+          <t>RIOX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GDXJ</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3541,57 +3541,57 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.00725582819096401</v>
+        <v>0.008306320764761553</v>
       </c>
       <c r="E53" t="n">
-        <v>680233.8929028759</v>
+        <v>778717.5716963956</v>
       </c>
       <c r="F53" t="n">
-        <v>451506.9618662666</v>
+        <v>518624.8623789623</v>
       </c>
       <c r="G53" t="n">
-        <v>-228726.9310366093</v>
+        <v>-260092.7093174334</v>
       </c>
       <c r="H53" t="n">
-        <v>228726.9310366093</v>
+        <v>260092.7093174334</v>
       </c>
       <c r="I53" t="n">
-        <v>212.9499969482422</v>
+        <v>55.54000091552734</v>
       </c>
       <c r="J53" t="n">
-        <v>1074.08750558565</v>
+        <v>4682.979924919649</v>
       </c>
       <c r="K53" t="n">
-        <v>0.003983652287543253</v>
+        <v>0.01904225095126328</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0004382685074647209</v>
+        <v>0.008092492511432278</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0004141697385296669</v>
+        <v>0.007336483180565754</v>
       </c>
       <c r="N53" t="n">
-        <v>269623.8095238095</v>
+        <v>245925.7540983607</v>
       </c>
       <c r="O53" t="n">
-        <v>57416389.41526867</v>
+        <v>13658716.6077747</v>
       </c>
       <c r="P53" t="n">
-        <v>521887671.9199838</v>
+        <v>32140000</v>
       </c>
       <c r="Q53" t="n">
-        <v>2593351</v>
+        <v>638314</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BABX</t>
+          <t>GLWG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3600,57 +3600,57 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.006875347874025292</v>
+        <v>0.007829902025362422</v>
       </c>
       <c r="E54" t="n">
-        <v>644563.8631898711</v>
+        <v>734053.3148777271</v>
       </c>
       <c r="F54" t="n">
-        <v>430138.0936656292</v>
+        <v>488796.6109426362</v>
       </c>
       <c r="G54" t="n">
-        <v>-214425.7695242419</v>
+        <v>-245256.7039350909</v>
       </c>
       <c r="H54" t="n">
-        <v>214425.7695242419</v>
+        <v>245256.7039350909</v>
       </c>
       <c r="I54" t="n">
-        <v>30.04999923706055</v>
+        <v>34.43000030517578</v>
       </c>
       <c r="J54" t="n">
-        <v>7135.633110425887</v>
+        <v>7123.343065966284</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01074312248223394</v>
+        <v>0.01129061400978209</v>
       </c>
       <c r="L54" t="n">
-        <v>0.001809058784950645</v>
+        <v>0.009511951297002625</v>
       </c>
       <c r="M54" t="n">
-        <v>0.001809058716411381</v>
+        <v>0.007837763001297557</v>
       </c>
       <c r="N54" t="n">
-        <v>664204.7619047619</v>
+        <v>630908.3863636364</v>
       </c>
       <c r="O54" t="n">
-        <v>19959352.58849008</v>
+        <v>21722175.93503796</v>
       </c>
       <c r="P54" t="n">
-        <v>118528912</v>
+        <v>25784058</v>
       </c>
       <c r="Q54" t="n">
-        <v>3944390</v>
+        <v>908849</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEVX</t>
+          <t>PTIR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3659,57 +3659,57 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.006677630759929053</v>
+        <v>0.007780550911757155</v>
       </c>
       <c r="E55" t="n">
-        <v>626027.8837433488</v>
+        <v>729426.6479772333</v>
       </c>
       <c r="F55" t="n">
-        <v>416863.8731374855</v>
+        <v>486041.0463832282</v>
       </c>
       <c r="G55" t="n">
-        <v>-209164.0106058633</v>
+        <v>-243385.6015940051</v>
       </c>
       <c r="H55" t="n">
-        <v>209164.0106058633</v>
+        <v>243385.6015940051</v>
       </c>
       <c r="I55" t="n">
-        <v>71.18000030517578</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="J55" t="n">
-        <v>2938.52219315956</v>
+        <v>17726.55569618196</v>
       </c>
       <c r="K55" t="n">
-        <v>0.033653317245783</v>
+        <v>0.003526659596345245</v>
       </c>
       <c r="L55" t="n">
-        <v>0.005405178751980728</v>
+        <v>0.0005963222157906338</v>
       </c>
       <c r="M55" t="n">
-        <v>0.005391783840659743</v>
+        <v>0.0006228582696172845</v>
       </c>
       <c r="N55" t="n">
-        <v>87317.46031746031</v>
+        <v>5026443.639344262</v>
       </c>
       <c r="O55" t="n">
-        <v>6215256.852043999</v>
+        <v>69013068.86727342</v>
       </c>
       <c r="P55" t="n">
-        <v>38696964.56</v>
+        <v>408144448</v>
       </c>
       <c r="Q55" t="n">
-        <v>545000</v>
+        <v>28460015</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SMCL</t>
+          <t>NUGT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3718,57 +3718,57 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.006655207703598331</v>
+        <v>0.007686903535314975</v>
       </c>
       <c r="E56" t="n">
-        <v>623925.7222123436</v>
+        <v>720647.2064357789</v>
       </c>
       <c r="F56" t="n">
-        <v>415254.9121078809</v>
+        <v>478900.4078997913</v>
       </c>
       <c r="G56" t="n">
-        <v>-208670.8101044627</v>
+        <v>-241746.7985359875</v>
       </c>
       <c r="H56" t="n">
-        <v>208670.8101044627</v>
+        <v>241746.7985359875</v>
       </c>
       <c r="I56" t="n">
-        <v>73.94999694824219</v>
+        <v>206.3000030517578</v>
       </c>
       <c r="J56" t="n">
-        <v>2821.782538415952</v>
+        <v>1171.821594570392</v>
       </c>
       <c r="K56" t="n">
-        <v>0.003812171749018475</v>
+        <v>0.001760986290359384</v>
       </c>
       <c r="L56" t="n">
-        <v>0.007429793763386278</v>
+        <v>0.0002182713575409372</v>
       </c>
       <c r="M56" t="n">
-        <v>0.007429790802926731</v>
+        <v>0.00019362845478986</v>
       </c>
       <c r="N56" t="n">
-        <v>740203.4126984127</v>
+        <v>665434.8196721311</v>
       </c>
       <c r="O56" t="n">
-        <v>54738040.11012607</v>
+        <v>137279205.3291066</v>
       </c>
       <c r="P56" t="n">
-        <v>28085680</v>
+        <v>1107551633.249211</v>
       </c>
       <c r="Q56" t="n">
-        <v>379793</v>
+        <v>6051908</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GDXU</t>
+          <t>ORCX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3777,57 +3777,57 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.006564143840037818</v>
+        <v>0.007473782430914704</v>
       </c>
       <c r="E57" t="n">
-        <v>615388.4850035454</v>
+        <v>700667.1028982535</v>
       </c>
       <c r="F57" t="n">
-        <v>463177.6304392255</v>
+        <v>466721.4925816413</v>
       </c>
       <c r="G57" t="n">
-        <v>-152210.8545643199</v>
+        <v>-233945.6103166122</v>
       </c>
       <c r="H57" t="n">
-        <v>152210.8545643199</v>
+        <v>233945.6103166122</v>
       </c>
       <c r="I57" t="n">
-        <v>203.9900054931641</v>
+        <v>44.25</v>
       </c>
       <c r="J57" t="n">
-        <v>746.1681968012922</v>
+        <v>5286.906447833044</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0006547222103625161</v>
+        <v>0.001747749981806216</v>
       </c>
       <c r="L57" t="n">
-        <v>0.0001056755681409899</v>
+        <v>0.0005497488199191921</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0001056755659805476</v>
+        <v>0.0005624382921651123</v>
       </c>
       <c r="N57" t="n">
-        <v>1139671.428571429</v>
+        <v>3024978.68852459</v>
       </c>
       <c r="O57" t="n">
-        <v>232481580.9746879</v>
+        <v>133855306.9672131</v>
       </c>
       <c r="P57" t="n">
-        <v>1440359936</v>
+        <v>425550000</v>
       </c>
       <c r="Q57" t="n">
-        <v>7060934</v>
+        <v>9399976</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VRTL</t>
+          <t>AVGG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3836,57 +3836,57 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.006521670293415978</v>
+        <v>0.007442740693603745</v>
       </c>
       <c r="E58" t="n">
-        <v>611406.5900077479</v>
+        <v>697756.940025351</v>
       </c>
       <c r="F58" t="n">
-        <v>406374.1989924065</v>
+        <v>465093.7389498755</v>
       </c>
       <c r="G58" t="n">
-        <v>-205032.3910153413</v>
+        <v>-232663.2010754755</v>
       </c>
       <c r="H58" t="n">
-        <v>205032.3910153413</v>
+        <v>232663.2010754755</v>
       </c>
       <c r="I58" t="n">
-        <v>177.9700012207031</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="J58" t="n">
-        <v>1152.061525026781</v>
+        <v>6186.205724533771</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01246391607306759</v>
+        <v>0.03631936692225773</v>
       </c>
       <c r="L58" t="n">
-        <v>0.003215473295829085</v>
+        <v>0.005954854731172067</v>
       </c>
       <c r="M58" t="n">
-        <v>0.003031732877089221</v>
+        <v>0.005701572096344489</v>
       </c>
       <c r="N58" t="n">
-        <v>92431.74603174604</v>
+        <v>170328.0163934426</v>
       </c>
       <c r="O58" t="n">
-        <v>16450077.95410156</v>
+        <v>6406036.800517348</v>
       </c>
       <c r="P58" t="n">
-        <v>63764296</v>
+        <v>39071180</v>
       </c>
       <c r="Q58" t="n">
-        <v>380001</v>
+        <v>1085000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MULL</t>
+          <t>YINN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>FXI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3895,57 +3895,57 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.006508240792919036</v>
+        <v>0.007425667763935604</v>
       </c>
       <c r="E59" t="n">
-        <v>610147.5743361596</v>
+        <v>696156.3528689629</v>
       </c>
       <c r="F59" t="n">
-        <v>406561.4634465501</v>
+        <v>520978.6093186451</v>
       </c>
       <c r="G59" t="n">
-        <v>-203586.1108896095</v>
+        <v>-175177.7435503178</v>
       </c>
       <c r="H59" t="n">
-        <v>203586.1108896095</v>
+        <v>175177.7435503178</v>
       </c>
       <c r="I59" t="n">
-        <v>475.9500122070312</v>
+        <v>36.59000015258789</v>
       </c>
       <c r="J59" t="n">
-        <v>427.7468340541874</v>
+        <v>4787.585209614383</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0009637762212737719</v>
+        <v>0.002119103393218716</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0007387423332822378</v>
+        <v>0.000225014134175798</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0003687469528510643</v>
+        <v>0.00022019208546982</v>
       </c>
       <c r="N59" t="n">
-        <v>443823.8095238095</v>
+        <v>2259250.409836065</v>
       </c>
       <c r="O59" t="n">
-        <v>211237947.5606283</v>
+        <v>82665972.8406359</v>
       </c>
       <c r="P59" t="n">
-        <v>275584736</v>
+        <v>778518843.6805296</v>
       </c>
       <c r="Q59" t="n">
-        <v>1160001</v>
+        <v>21742767</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>URAA</t>
+          <t>IONL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3954,57 +3954,57 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.006287881134807937</v>
+        <v>0.007196172279635133</v>
       </c>
       <c r="E60" t="n">
-        <v>589488.8563882441</v>
+        <v>674641.1512157937</v>
       </c>
       <c r="F60" t="n">
-        <v>388503.9070571005</v>
+        <v>448479.1829905863</v>
       </c>
       <c r="G60" t="n">
-        <v>-200984.9493311436</v>
+        <v>-226161.9682252074</v>
       </c>
       <c r="H60" t="n">
-        <v>200984.9493311436</v>
+        <v>226161.9682252074</v>
       </c>
       <c r="I60" t="n">
-        <v>40.97999954223633</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="J60" t="n">
-        <v>4904.464411328189</v>
+        <v>6230.35738233038</v>
       </c>
       <c r="K60" t="n">
-        <v>0.05832145905239357</v>
+        <v>0.006349394264678107</v>
       </c>
       <c r="L60" t="n">
-        <v>0.00366625231868867</v>
+        <v>0.002209864054839339</v>
       </c>
       <c r="M60" t="n">
-        <v>0.00392356839020784</v>
+        <v>0.001683879918500125</v>
       </c>
       <c r="N60" t="n">
-        <v>84093.6507936508</v>
+        <v>981252.2459016393</v>
       </c>
       <c r="O60" t="n">
-        <v>3446157.771028792</v>
+        <v>35619455.77759346</v>
       </c>
       <c r="P60" t="n">
-        <v>54820272</v>
+        <v>102342027.66</v>
       </c>
       <c r="Q60" t="n">
-        <v>1250001</v>
+        <v>3700001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NVOX</t>
+          <t>QUBX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4013,57 +4013,57 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.006234293570008666</v>
+        <v>0.007106553807049267</v>
       </c>
       <c r="E61" t="n">
-        <v>584465.0221883125</v>
+        <v>666239.4194108688</v>
       </c>
       <c r="F61" t="n">
-        <v>390032.2137424334</v>
+        <v>443342.3235892332</v>
       </c>
       <c r="G61" t="n">
-        <v>-194432.8084458791</v>
+        <v>-222897.0958216356</v>
       </c>
       <c r="H61" t="n">
-        <v>194432.8084458791</v>
+        <v>222897.0958216356</v>
       </c>
       <c r="I61" t="n">
-        <v>15.4399995803833</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="J61" t="n">
-        <v>12592.79881671164</v>
+        <v>14869.71976151063</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01150816353682866</v>
+        <v>0.06900003822182503</v>
       </c>
       <c r="L61" t="n">
-        <v>0.003710549779501509</v>
+        <v>0.007766353884086885</v>
       </c>
       <c r="M61" t="n">
-        <v>0.003716771966571139</v>
+        <v>0.006932328458472207</v>
       </c>
       <c r="N61" t="n">
-        <v>1094249.206349206</v>
+        <v>215503.0655737705</v>
       </c>
       <c r="O61" t="n">
-        <v>16895207.28686651</v>
+        <v>3230390.903626082</v>
       </c>
       <c r="P61" t="n">
-        <v>52400000</v>
+        <v>28700352.72</v>
       </c>
       <c r="Q61" t="n">
-        <v>3388101</v>
+        <v>2144982</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PTIR</t>
+          <t>ETHT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ETHA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4072,57 +4072,57 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.006162595381249774</v>
+        <v>0.007082963125467222</v>
       </c>
       <c r="E62" t="n">
-        <v>577743.3169921663</v>
+        <v>664027.7930125521</v>
       </c>
       <c r="F62" t="n">
-        <v>384969.4374485673</v>
+        <v>442019.1694710769</v>
       </c>
       <c r="G62" t="n">
-        <v>-192773.8795435991</v>
+        <v>-222008.6235414751</v>
       </c>
       <c r="H62" t="n">
-        <v>192773.8795435991</v>
+        <v>222008.6235414751</v>
       </c>
       <c r="I62" t="n">
-        <v>13.93000030517578</v>
+        <v>17.95000076293945</v>
       </c>
       <c r="J62" t="n">
-        <v>13838.75630440386</v>
+        <v>12368.16791673046</v>
       </c>
       <c r="K62" t="n">
-        <v>0.002726199650900023</v>
+        <v>0.005892811050740257</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0004723177798650321</v>
+        <v>0.0008424588607680221</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0004862526005135226</v>
+        <v>0.0008267547187301027</v>
       </c>
       <c r="N62" t="n">
-        <v>5076207.936507937</v>
+        <v>2098857.032786885</v>
       </c>
       <c r="O62" t="n">
-        <v>70711578.10469128</v>
+        <v>37674485.33982543</v>
       </c>
       <c r="P62" t="n">
-        <v>408144448</v>
+        <v>263524587.2292</v>
       </c>
       <c r="Q62" t="n">
-        <v>28460015</v>
+        <v>14959900</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COHX</t>
+          <t>SOUX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4131,57 +4131,57 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.006085105888541729</v>
+        <v>0.007004188751220702</v>
       </c>
       <c r="E63" t="n">
-        <v>570478.6770507871</v>
+        <v>656642.6954269408</v>
       </c>
       <c r="F63" t="n">
-        <v>380572.3265012575</v>
+        <v>437542.6969528198</v>
       </c>
       <c r="G63" t="n">
-        <v>-189906.3505495297</v>
+        <v>-219099.9984741211</v>
       </c>
       <c r="H63" t="n">
-        <v>189906.3505495297</v>
+        <v>219099.9984741211</v>
       </c>
       <c r="I63" t="n">
-        <v>47.20000076293945</v>
+        <v>21.90999984741211</v>
       </c>
       <c r="J63" t="n">
-        <v>4023.439565251883</v>
+        <v>9999.999999999998</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00659366001252829</v>
+        <v>0.06089526015253763</v>
       </c>
       <c r="L63" t="n">
-        <v>0.00159513005890699</v>
+        <v>0.01025269061647735</v>
       </c>
       <c r="M63" t="n">
-        <v>0.001593441411980944</v>
+        <v>0.01142878041198468</v>
       </c>
       <c r="N63" t="n">
-        <v>610198.2142857143</v>
+        <v>164216.3934426229</v>
       </c>
       <c r="O63" t="n">
-        <v>28801356.17983001</v>
+        <v>3597981.155270435</v>
       </c>
       <c r="P63" t="n">
-        <v>119053834.82</v>
+        <v>21370000</v>
       </c>
       <c r="Q63" t="n">
-        <v>2525000</v>
+        <v>874984</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUBX</t>
+          <t>ROBN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4190,57 +4190,57 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.006062617574188477</v>
+        <v>0.006723316527067754</v>
       </c>
       <c r="E64" t="n">
-        <v>568370.3975801697</v>
+        <v>630310.924412602</v>
       </c>
       <c r="F64" t="n">
-        <v>378152.7277072883</v>
+        <v>421044.3492424154</v>
       </c>
       <c r="G64" t="n">
-        <v>-190217.6698728814</v>
+        <v>-209266.5751701866</v>
       </c>
       <c r="H64" t="n">
-        <v>190217.6698728814</v>
+        <v>209266.5751701866</v>
       </c>
       <c r="I64" t="n">
-        <v>13.42000007629395</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="J64" t="n">
-        <v>14174.19290547513</v>
+        <v>9706.242131441519</v>
       </c>
       <c r="K64" t="n">
-        <v>0.06914133370330568</v>
+        <v>0.006025724052199024</v>
       </c>
       <c r="L64" t="n">
-        <v>0.006627711921474999</v>
+        <v>0.001329031076034159</v>
       </c>
       <c r="M64" t="n">
-        <v>0.006608070792890166</v>
+        <v>0.001190949954778101</v>
       </c>
       <c r="N64" t="n">
-        <v>205003.1746031746</v>
+        <v>1610800.967213115</v>
       </c>
       <c r="O64" t="n">
-        <v>2751142.618815104</v>
+        <v>34728867.99285423</v>
       </c>
       <c r="P64" t="n">
-        <v>28700352.72</v>
+        <v>157458000</v>
       </c>
       <c r="Q64" t="n">
-        <v>2144982</v>
+        <v>8150000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LRCU</t>
+          <t>DLLL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4249,57 +4249,57 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.006001577089649988</v>
+        <v>0.006628122157330856</v>
       </c>
       <c r="E65" t="n">
-        <v>562647.8521546863</v>
+        <v>621386.4522497677</v>
       </c>
       <c r="F65" t="n">
-        <v>377870.2323994527</v>
+        <v>413286.5017307564</v>
       </c>
       <c r="G65" t="n">
-        <v>-184777.6197552336</v>
+        <v>-208099.9505190113</v>
       </c>
       <c r="H65" t="n">
-        <v>184777.6197552336</v>
+        <v>208099.9505190113</v>
       </c>
       <c r="I65" t="n">
-        <v>56.54000091552734</v>
+        <v>75.47080230712891</v>
       </c>
       <c r="J65" t="n">
-        <v>3268.086607060682</v>
+        <v>2757.357072635153</v>
       </c>
       <c r="K65" t="n">
-        <v>0.03000647908545113</v>
+        <v>0.02305865886067524</v>
       </c>
       <c r="L65" t="n">
-        <v>0.006181593981956996</v>
+        <v>0.008711756198326476</v>
       </c>
       <c r="M65" t="n">
-        <v>0.006166201145397513</v>
+        <v>0.009676668711366429</v>
       </c>
       <c r="N65" t="n">
-        <v>108912.6984126984</v>
+        <v>119580.1147540984</v>
       </c>
       <c r="O65" t="n">
-        <v>6157924.067966522</v>
+        <v>9024807.200470347</v>
       </c>
       <c r="P65" t="n">
-        <v>29891581.41</v>
+        <v>23887256</v>
       </c>
       <c r="Q65" t="n">
-        <v>530000</v>
+        <v>284949</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SOXL</t>
+          <t>XRPT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>XRPZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4308,57 +4308,57 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.005454376294704175</v>
+        <v>0.006524421727885898</v>
       </c>
       <c r="E66" t="n">
-        <v>511347.7776285164</v>
+        <v>611664.536989303</v>
       </c>
       <c r="F66" t="n">
-        <v>382219.5509546487</v>
+        <v>408992.3908695869</v>
       </c>
       <c r="G66" t="n">
-        <v>-129128.2266738678</v>
+        <v>-202672.146119716</v>
       </c>
       <c r="H66" t="n">
-        <v>129128.2266738678</v>
+        <v>202672.146119716</v>
       </c>
       <c r="I66" t="n">
-        <v>176.9400024414062</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="J66" t="n">
-        <v>729.7853786151533</v>
+        <v>4261.399080478868</v>
       </c>
       <c r="K66" t="n">
-        <v>8.827467894923248e-06</v>
+        <v>0.0248283516782634</v>
       </c>
       <c r="L66" t="n">
-        <v>6.711569447960399e-06</v>
+        <v>0.00286010149604453</v>
       </c>
       <c r="M66" t="n">
-        <v>5.76449472942709e-06</v>
+        <v>0.002629177048082021</v>
       </c>
       <c r="N66" t="n">
-        <v>82672107.93650794</v>
+        <v>171634.3934426229</v>
       </c>
       <c r="O66" t="n">
-        <v>14628002980.12192</v>
+        <v>8162931.987835118</v>
       </c>
       <c r="P66" t="n">
-        <v>19239646952.19074</v>
+        <v>70861872</v>
       </c>
       <c r="Q66" t="n">
-        <v>126600060</v>
+        <v>1620811</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NUGT</t>
+          <t>QCMU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4367,57 +4367,57 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.005197992655273969</v>
+        <v>0.006416032367798021</v>
       </c>
       <c r="E67" t="n">
-        <v>487311.8114319346</v>
+        <v>601503.0344810644</v>
       </c>
       <c r="F67" t="n">
-        <v>323839.2145074345</v>
+        <v>400801.3212741694</v>
       </c>
       <c r="G67" t="n">
-        <v>-163472.5969245</v>
+        <v>-200701.713206895</v>
       </c>
       <c r="H67" t="n">
-        <v>163472.5969245</v>
+        <v>200701.713206895</v>
       </c>
       <c r="I67" t="n">
-        <v>193.8899993896484</v>
+        <v>46.13000106811523</v>
       </c>
       <c r="J67" t="n">
-        <v>843.120312750012</v>
+        <v>4350.784924338942</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00126635386530417</v>
+        <v>0.02825366075031372</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0001475981724165061</v>
+        <v>0.006158848329340576</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0001393147934089566</v>
+        <v>0.00527367230383835</v>
       </c>
       <c r="N67" t="n">
-        <v>665785.7142857143</v>
+        <v>153990.131147541</v>
       </c>
       <c r="O67" t="n">
-        <v>129089191.7364938</v>
+        <v>7103564.914315271</v>
       </c>
       <c r="P67" t="n">
-        <v>1107551633.249211</v>
+        <v>32587539.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>6051908</v>
+        <v>825001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QBTX</t>
+          <t>QPUX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>QBTS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4426,57 +4426,57 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.00506214399497067</v>
+        <v>0.006205045904981493</v>
       </c>
       <c r="E68" t="n">
-        <v>474575.9995285003</v>
+        <v>581723.0535920149</v>
       </c>
       <c r="F68" t="n">
-        <v>316014.0217374879</v>
+        <v>384528.7981370947</v>
       </c>
       <c r="G68" t="n">
-        <v>-158561.9777910125</v>
+        <v>-197194.2554549203</v>
       </c>
       <c r="H68" t="n">
-        <v>158561.9777910125</v>
+        <v>197194.2554549203</v>
       </c>
       <c r="I68" t="n">
-        <v>16.78000068664551</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="J68" t="n">
-        <v>9449.461936983425</v>
+        <v>5517.466317684284</v>
       </c>
       <c r="K68" t="n">
-        <v>0.005105390505327848</v>
+        <v>0.04242843190662535</v>
       </c>
       <c r="L68" t="n">
-        <v>0.001966458650632028</v>
+        <v>0.005471538719614882</v>
       </c>
       <c r="M68" t="n">
-        <v>0.001976874882214106</v>
+        <v>0.004662708010597561</v>
       </c>
       <c r="N68" t="n">
-        <v>1850879.365079365</v>
+        <v>130041.7213114754</v>
       </c>
       <c r="O68" t="n">
-        <v>31057757.01692975</v>
+        <v>4647691.337942842</v>
       </c>
       <c r="P68" t="n">
-        <v>80633263.12</v>
+        <v>36040000</v>
       </c>
       <c r="Q68" t="n">
-        <v>4780000</v>
+        <v>1183318</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HOOG</t>
+          <t>QBTX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>QBTS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4485,57 +4485,57 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.005054051054326653</v>
+        <v>0.006100931394856769</v>
       </c>
       <c r="E69" t="n">
-        <v>473817.2863431237</v>
+        <v>571962.3182678221</v>
       </c>
       <c r="F69" t="n">
-        <v>316245.8575625704</v>
+        <v>380862.3121643066</v>
       </c>
       <c r="G69" t="n">
-        <v>-157571.4287805533</v>
+        <v>-191100.0061035156</v>
       </c>
       <c r="H69" t="n">
-        <v>157571.4287805533</v>
+        <v>191100.0061035156</v>
       </c>
       <c r="I69" t="n">
-        <v>19.54800033569336</v>
+        <v>19.11000061035156</v>
       </c>
       <c r="J69" t="n">
-        <v>8060.744120862236</v>
+        <v>9999.999999999998</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0113587474191268</v>
+        <v>0.005326049765281859</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00248563102781044</v>
+        <v>0.002369989737598946</v>
       </c>
       <c r="M69" t="n">
-        <v>0.002245332624195609</v>
+        <v>0.002092050209205021</v>
       </c>
       <c r="N69" t="n">
-        <v>709650.7936507936</v>
+        <v>1877564.131147541</v>
       </c>
       <c r="O69" t="n">
-        <v>13872253.95251077</v>
+        <v>35880251.69220371</v>
       </c>
       <c r="P69" t="n">
-        <v>63392928</v>
+        <v>80633263.12</v>
       </c>
       <c r="Q69" t="n">
-        <v>3590000</v>
+        <v>4780000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SOFX</t>
+          <t>TQQQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4544,57 +4544,57 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.005051037013899314</v>
+        <v>0.005875646232299149</v>
       </c>
       <c r="E70" t="n">
-        <v>473534.7200530606</v>
+        <v>550841.8342780452</v>
       </c>
       <c r="F70" t="n">
-        <v>315899.9930047715</v>
+        <v>412820.8284454105</v>
       </c>
       <c r="G70" t="n">
-        <v>-157634.7270482891</v>
+        <v>-138021.0058326347</v>
       </c>
       <c r="H70" t="n">
-        <v>157634.7270482891</v>
+        <v>138021.0058326347</v>
       </c>
       <c r="I70" t="n">
-        <v>8.520000457763672</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="J70" t="n">
-        <v>18501.72753273127</v>
+        <v>1793.412259284728</v>
       </c>
       <c r="K70" t="n">
-        <v>0.02053082479465931</v>
+        <v>1.829461557853284e-05</v>
       </c>
       <c r="L70" t="n">
-        <v>0.002812394773386068</v>
+        <v>3.918382695877286e-06</v>
       </c>
       <c r="M70" t="n">
-        <v>0.002816092470735353</v>
+        <v>3.885629421048052e-06</v>
       </c>
       <c r="N70" t="n">
-        <v>901168.253968254</v>
+        <v>98029513.19672132</v>
       </c>
       <c r="O70" t="n">
-        <v>7677953.936331613</v>
+        <v>7544351245.870973</v>
       </c>
       <c r="P70" t="n">
-        <v>56050000</v>
+        <v>35223972885</v>
       </c>
       <c r="Q70" t="n">
-        <v>6570000</v>
+        <v>461550000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ORCX</t>
+          <t>AMUU</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4603,57 +4603,57 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.004930180025847335</v>
+        <v>0.005854824379365473</v>
       </c>
       <c r="E71" t="n">
-        <v>462204.3774231876</v>
+        <v>548889.7855655131</v>
       </c>
       <c r="F71" t="n">
-        <v>307879.0427242936</v>
+        <v>366413.1281301696</v>
       </c>
       <c r="G71" t="n">
-        <v>-154325.334698894</v>
+        <v>-182476.6574353435</v>
       </c>
       <c r="H71" t="n">
-        <v>154325.334698894</v>
+        <v>182476.6574353435</v>
       </c>
       <c r="I71" t="n">
-        <v>45.22999954223633</v>
+        <v>198.3999938964844</v>
       </c>
       <c r="J71" t="n">
-        <v>3412.01274067631</v>
+        <v>919.7412452066458</v>
       </c>
       <c r="K71" t="n">
-        <v>0.001097167329487754</v>
+        <v>0.005961391358311498</v>
       </c>
       <c r="L71" t="n">
-        <v>0.0003626491239546329</v>
+        <v>0.001497779637598389</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0003629810055553663</v>
+        <v>0.001471583637796813</v>
       </c>
       <c r="N71" t="n">
-        <v>3109838.079365079</v>
+        <v>154282.9836065574</v>
       </c>
       <c r="O71" t="n">
-        <v>140657974.9061116</v>
+        <v>30609743.00587238</v>
       </c>
       <c r="P71" t="n">
-        <v>425550000</v>
+        <v>121831444.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>9399976</v>
+        <v>625001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PLTU</t>
+          <t>AMDL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4662,57 +4662,57 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.004469023406126626</v>
+        <v>0.005831610961507052</v>
       </c>
       <c r="E72" t="n">
-        <v>418970.9443243712</v>
+        <v>546713.5276412861</v>
       </c>
       <c r="F72" t="n">
-        <v>278940.5484940332</v>
+        <v>364293.2648313809</v>
       </c>
       <c r="G72" t="n">
-        <v>-140030.395830338</v>
+        <v>-182420.2628099053</v>
       </c>
       <c r="H72" t="n">
-        <v>140030.395830338</v>
+        <v>182420.2628099053</v>
       </c>
       <c r="I72" t="n">
-        <v>37.75</v>
+        <v>56.59000015258789</v>
       </c>
       <c r="J72" t="n">
-        <v>3709.4144590818</v>
+        <v>3223.542362926873</v>
       </c>
       <c r="K72" t="n">
-        <v>0.001339916592017218</v>
+        <v>0.0002616929850936557</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0002398352111257142</v>
+        <v>0.000122664893878347</v>
       </c>
       <c r="M72" t="n">
-        <v>0.0002374025101874746</v>
+        <v>0.0001208224273960597</v>
       </c>
       <c r="N72" t="n">
-        <v>2768392.063492063</v>
+        <v>12318031.2295082</v>
       </c>
       <c r="O72" t="n">
-        <v>104506800.3968254</v>
+        <v>697077389.1574513</v>
       </c>
       <c r="P72" t="n">
-        <v>583860873.3599938</v>
+        <v>1487143200</v>
       </c>
       <c r="Q72" t="n">
-        <v>15625001</v>
+        <v>26680000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AVGG</t>
+          <t>SOFX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4721,57 +4721,57 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.004375498022865903</v>
+        <v>0.005822216730143228</v>
       </c>
       <c r="E73" t="n">
-        <v>410202.9396436784</v>
+        <v>545832.8184509276</v>
       </c>
       <c r="F73" t="n">
-        <v>273423.0331269467</v>
+        <v>364130.8149719238</v>
       </c>
       <c r="G73" t="n">
-        <v>-136779.9065167317</v>
+        <v>-181702.0034790039</v>
       </c>
       <c r="H73" t="n">
-        <v>136779.9065167317</v>
+        <v>181702.0034790039</v>
       </c>
       <c r="I73" t="n">
-        <v>37.97000122070312</v>
+        <v>9.085100173950195</v>
       </c>
       <c r="J73" t="n">
-        <v>3602.315041331959</v>
+        <v>20000</v>
       </c>
       <c r="K73" t="n">
-        <v>0.02093229485642861</v>
+        <v>0.02137423020140534</v>
       </c>
       <c r="L73" t="n">
-        <v>0.003500787703794246</v>
+        <v>0.0032417841833899</v>
       </c>
       <c r="M73" t="n">
-        <v>0.003320106028877381</v>
+        <v>0.0030441400304414</v>
       </c>
       <c r="N73" t="n">
-        <v>172093.6507936508</v>
+        <v>935706.2131147541</v>
       </c>
       <c r="O73" t="n">
-        <v>6534396.130710178</v>
+        <v>8500984.67953513</v>
       </c>
       <c r="P73" t="n">
-        <v>39071180</v>
+        <v>56050000</v>
       </c>
       <c r="Q73" t="n">
-        <v>1085000</v>
+        <v>6570000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QCMU</t>
+          <t>PLTU</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4780,57 +4780,57 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.004212058776796392</v>
+        <v>0.005761622216564694</v>
       </c>
       <c r="E74" t="n">
-        <v>394880.5103246618</v>
+        <v>540152.08280294</v>
       </c>
       <c r="F74" t="n">
-        <v>263209.7833074355</v>
+        <v>359619.9695666633</v>
       </c>
       <c r="G74" t="n">
-        <v>-131670.7270172263</v>
+        <v>-180532.1132362768</v>
       </c>
       <c r="H74" t="n">
-        <v>131670.7270172263</v>
+        <v>180532.1132362768</v>
       </c>
       <c r="I74" t="n">
-        <v>39.5</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="J74" t="n">
-        <v>3333.436127018388</v>
+        <v>4853.013697143041</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02447542347029339</v>
+        <v>0.001772703819903132</v>
       </c>
       <c r="L74" t="n">
-        <v>0.004040523741205632</v>
+        <v>0.0003092039927206515</v>
       </c>
       <c r="M74" t="n">
-        <v>0.004040523741205632</v>
+        <v>0.0003105928567392118</v>
       </c>
       <c r="N74" t="n">
-        <v>136195.2380952381</v>
+        <v>2737633.68852459</v>
       </c>
       <c r="O74" t="n">
-        <v>5379711.904761905</v>
+        <v>101839975.3017635</v>
       </c>
       <c r="P74" t="n">
-        <v>32587539.5</v>
+        <v>583860873.3599938</v>
       </c>
       <c r="Q74" t="n">
-        <v>825001</v>
+        <v>15625001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DLLL</t>
+          <t>MVLL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4839,57 +4839,57 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.004160731327566412</v>
+        <v>0.005694264445138293</v>
       </c>
       <c r="E75" t="n">
-        <v>390068.5619593512</v>
+        <v>533837.291731715</v>
       </c>
       <c r="F75" t="n">
-        <v>259436.0897693474</v>
+        <v>355415.7370085482</v>
       </c>
       <c r="G75" t="n">
-        <v>-130632.4721900037</v>
+        <v>-178421.5547231668</v>
       </c>
       <c r="H75" t="n">
-        <v>130632.4721900037</v>
+        <v>178421.5547231668</v>
       </c>
       <c r="I75" t="n">
-        <v>83.83000183105469</v>
+        <v>72.48999786376953</v>
       </c>
       <c r="J75" t="n">
-        <v>1558.302151218744</v>
+        <v>2461.326527536591</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01447104782163896</v>
+        <v>0.003555009617687314</v>
       </c>
       <c r="L75" t="n">
-        <v>0.005468709850558128</v>
+        <v>0.0006229783921470949</v>
       </c>
       <c r="M75" t="n">
-        <v>0.005468705456831726</v>
+        <v>0.0006184235952545216</v>
       </c>
       <c r="N75" t="n">
-        <v>107684.126984127</v>
+        <v>692354.393442623</v>
       </c>
       <c r="O75" t="n">
-        <v>9027160.562254891</v>
+        <v>50188768.50162719</v>
       </c>
       <c r="P75" t="n">
-        <v>23887256</v>
+        <v>286400871.96</v>
       </c>
       <c r="Q75" t="n">
-        <v>284949</v>
+        <v>3980001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YINN</t>
+          <t>AMDG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FXI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4898,46 +4898,46 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.003889522750309868</v>
+        <v>0.005612381741008401</v>
       </c>
       <c r="E76" t="n">
-        <v>364642.7578415501</v>
+        <v>526160.7882195376</v>
       </c>
       <c r="F76" t="n">
-        <v>272885.6471617438</v>
+        <v>350949.0705307139</v>
       </c>
       <c r="G76" t="n">
-        <v>-91757.11067980627</v>
+        <v>-175211.7176888237</v>
       </c>
       <c r="H76" t="n">
-        <v>91757.11067980627</v>
+        <v>175211.7176888237</v>
       </c>
       <c r="I76" t="n">
-        <v>35.95999908447266</v>
+        <v>95.94000244140625</v>
       </c>
       <c r="J76" t="n">
-        <v>2551.643854724861</v>
+        <v>1826.26342745646</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00115337306861945</v>
+        <v>0.01624855644683693</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0001178611300479445</v>
+        <v>0.006805699690960472</v>
       </c>
       <c r="M76" t="n">
-        <v>0.0001173559857733315</v>
+        <v>0.006688654102368013</v>
       </c>
       <c r="N76" t="n">
-        <v>2212331.746031746</v>
+        <v>112395.4262295082</v>
       </c>
       <c r="O76" t="n">
-        <v>79555447.56185137</v>
+        <v>10783217.46686191</v>
       </c>
       <c r="P76" t="n">
-        <v>778518843.6805296</v>
+        <v>25744850</v>
       </c>
       <c r="Q76" t="n">
-        <v>21742767</v>
+        <v>273039</v>
       </c>
     </row>
     <row r="77">
@@ -4957,40 +4957,40 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.003876704544312927</v>
+        <v>0.005562742557978053</v>
       </c>
       <c r="E77" t="n">
-        <v>363441.0510293369</v>
+        <v>521507.1148104425</v>
       </c>
       <c r="F77" t="n">
-        <v>242010.6965257162</v>
+        <v>347264.8445764156</v>
       </c>
       <c r="G77" t="n">
-        <v>-121430.3545036208</v>
+        <v>-174242.2702340269</v>
       </c>
       <c r="H77" t="n">
-        <v>121430.3545036208</v>
+        <v>174242.2702340269</v>
       </c>
       <c r="I77" t="n">
-        <v>15.61999988555908</v>
+        <v>16.83499908447266</v>
       </c>
       <c r="J77" t="n">
-        <v>7774.0304349096</v>
+        <v>10350.00176476011</v>
       </c>
       <c r="K77" t="n">
-        <v>9.388835832570822e-05</v>
+        <v>0.0001220129900165769</v>
       </c>
       <c r="L77" t="n">
-        <v>2.214193412258501e-05</v>
+        <v>3.177179943731813e-05</v>
       </c>
       <c r="M77" t="n">
-        <v>2.052278356490712e-05</v>
+        <v>2.732313024666574e-05</v>
       </c>
       <c r="N77" t="n">
-        <v>82800792.06349206</v>
+        <v>84827048.03278689</v>
       </c>
       <c r="O77" t="n">
-        <v>1293348362.555947</v>
+        <v>1428063275.970485</v>
       </c>
       <c r="P77" t="n">
         <v>5484180100.588434</v>
@@ -5002,12 +5002,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GLWG</t>
+          <t>FBL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5016,57 +5016,57 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.003857289468810098</v>
+        <v>0.005306158318748909</v>
       </c>
       <c r="E78" t="n">
-        <v>361620.8877009467</v>
+        <v>497452.3423827103</v>
       </c>
       <c r="F78" t="n">
-        <v>240798.6733003631</v>
+        <v>331468.9114909151</v>
       </c>
       <c r="G78" t="n">
-        <v>-120822.2144005836</v>
+        <v>-165983.4308917952</v>
       </c>
       <c r="H78" t="n">
-        <v>120822.2144005836</v>
+        <v>165983.4308917952</v>
       </c>
       <c r="I78" t="n">
-        <v>28.3700008392334</v>
+        <v>24.43000030517578</v>
       </c>
       <c r="J78" t="n">
-        <v>4258.801932550397</v>
+        <v>6794.245960636755</v>
       </c>
       <c r="K78" t="n">
-        <v>0.007235877538669656</v>
+        <v>0.005296201277228326</v>
       </c>
       <c r="L78" t="n">
-        <v>0.004685927032920248</v>
+        <v>0.0008953231615680829</v>
       </c>
       <c r="M78" t="n">
-        <v>0.004685929051526048</v>
+        <v>0.0009286732537073491</v>
       </c>
       <c r="N78" t="n">
-        <v>588567.4418604651</v>
+        <v>1282852.672131147</v>
       </c>
       <c r="O78" t="n">
-        <v>16697658.81952685</v>
+        <v>31340091.1716595</v>
       </c>
       <c r="P78" t="n">
-        <v>25784058</v>
+        <v>185389408</v>
       </c>
       <c r="Q78" t="n">
-        <v>908849</v>
+        <v>7316078</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MVLL</t>
+          <t>URTY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5075,57 +5075,57 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.003727418973414704</v>
+        <v>0.005001474379000998</v>
       </c>
       <c r="E79" t="n">
-        <v>349445.5287576285</v>
+        <v>468888.2230313435</v>
       </c>
       <c r="F79" t="n">
-        <v>232652.2370605601</v>
+        <v>351578.1847447928</v>
       </c>
       <c r="G79" t="n">
-        <v>-116793.2916970683</v>
+        <v>-117310.0382865508</v>
       </c>
       <c r="H79" t="n">
-        <v>116793.2916970683</v>
+        <v>117310.0382865508</v>
       </c>
       <c r="I79" t="n">
-        <v>71.95999908447266</v>
+        <v>76.83000183105469</v>
       </c>
       <c r="J79" t="n">
-        <v>1623.030755739263</v>
+        <v>1526.877983740124</v>
       </c>
       <c r="K79" t="n">
-        <v>0.002441749294026273</v>
+        <v>0.001187912823774393</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0004077965646465637</v>
+        <v>0.000335506910669479</v>
       </c>
       <c r="M79" t="n">
-        <v>0.0004077965698348476</v>
+        <v>0.0003319299964652443</v>
       </c>
       <c r="N79" t="n">
-        <v>664700</v>
+        <v>1285345.147540984</v>
       </c>
       <c r="O79" t="n">
-        <v>47831811.39144897</v>
+        <v>98753070.03911102</v>
       </c>
       <c r="P79" t="n">
-        <v>286400871.96</v>
+        <v>349650140</v>
       </c>
       <c r="Q79" t="n">
-        <v>3980001</v>
+        <v>4600000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBL</t>
+          <t>BITX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>IBIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5134,57 +5134,57 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.003511076060584003</v>
+        <v>0.004999006771087676</v>
       </c>
       <c r="E80" t="n">
-        <v>329163.3806797503</v>
+        <v>468656.8847894696</v>
       </c>
       <c r="F80" t="n">
-        <v>219332.4228286491</v>
+        <v>312697.8549094464</v>
       </c>
       <c r="G80" t="n">
-        <v>-109830.9578511012</v>
+        <v>-155959.0298800232</v>
       </c>
       <c r="H80" t="n">
-        <v>109830.9578511012</v>
+        <v>155959.0298800232</v>
       </c>
       <c r="I80" t="n">
-        <v>25.34000015258789</v>
+        <v>21.05999946594238</v>
       </c>
       <c r="J80" t="n">
-        <v>4334.291917511473</v>
+        <v>7405.46219539253</v>
       </c>
       <c r="K80" t="n">
-        <v>0.003365568979561129</v>
+        <v>0.0006400869214109834</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0005924338344675074</v>
+        <v>0.0001180492757212724</v>
       </c>
       <c r="M80" t="n">
-        <v>0.0005924338036734263</v>
+        <v>0.0001130604915327104</v>
       </c>
       <c r="N80" t="n">
-        <v>1287833.333333333</v>
+        <v>11569463.37704918</v>
       </c>
       <c r="O80" t="n">
-        <v>32633696.86317443</v>
+        <v>243652892.5418957</v>
       </c>
       <c r="P80" t="n">
-        <v>185389408</v>
+        <v>1321135000</v>
       </c>
       <c r="Q80" t="n">
-        <v>7316078</v>
+        <v>65500000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BITX</t>
+          <t>CWEB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IBIT</t>
+          <t>KWEB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5193,57 +5193,57 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.00342185843549232</v>
+        <v>0.004933666797090378</v>
       </c>
       <c r="E81" t="n">
-        <v>320799.2283274049</v>
+        <v>462531.2622272229</v>
       </c>
       <c r="F81" t="n">
-        <v>214044.0774696995</v>
+        <v>307683.1664029099</v>
       </c>
       <c r="G81" t="n">
-        <v>-106755.1508577055</v>
+        <v>-154848.095824313</v>
       </c>
       <c r="H81" t="n">
-        <v>106755.1508577055</v>
+        <v>154848.095824313</v>
       </c>
       <c r="I81" t="n">
-        <v>20.17000007629395</v>
+        <v>28.5</v>
       </c>
       <c r="J81" t="n">
-        <v>5292.768986311316</v>
+        <v>5433.266520151334</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0004446696709264445</v>
+        <v>0.01103093887666067</v>
       </c>
       <c r="L81" t="n">
-        <v>8.080563368444972e-05</v>
+        <v>0.0005856454043227886</v>
       </c>
       <c r="M81" t="n">
-        <v>8.080563337879872e-05</v>
+        <v>0.0005827129798500737</v>
       </c>
       <c r="N81" t="n">
-        <v>11902698.41269841</v>
+        <v>492547.9672131148</v>
       </c>
       <c r="O81" t="n">
-        <v>240077427.8922308</v>
+        <v>14037617.06557377</v>
       </c>
       <c r="P81" t="n">
-        <v>1321135000</v>
+        <v>264405892.5099424</v>
       </c>
       <c r="Q81" t="n">
-        <v>65500000</v>
+        <v>9324087</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CWEB</t>
+          <t>TSLR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KWEB</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5252,57 +5252,57 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.003368523821038443</v>
+        <v>0.004788096363711389</v>
       </c>
       <c r="E82" t="n">
-        <v>315799.108222354</v>
+        <v>448884.0340979428</v>
       </c>
       <c r="F82" t="n">
-        <v>210074.5992761357</v>
+        <v>299206.1300972949</v>
       </c>
       <c r="G82" t="n">
-        <v>-105724.5089462183</v>
+        <v>-149677.9040006478</v>
       </c>
       <c r="H82" t="n">
-        <v>105724.5089462183</v>
+        <v>149677.9040006478</v>
       </c>
       <c r="I82" t="n">
-        <v>28.42000007629395</v>
+        <v>28.71999931335449</v>
       </c>
       <c r="J82" t="n">
-        <v>3720.074196425023</v>
+        <v>5211.626308467534</v>
       </c>
       <c r="K82" t="n">
-        <v>0.007832939211199598</v>
+        <v>0.002580016143799099</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0003998568562243474</v>
+        <v>0.0009714807057584557</v>
       </c>
       <c r="M82" t="n">
-        <v>0.0003989746338086531</v>
+        <v>0.0009001080152607114</v>
       </c>
       <c r="N82" t="n">
-        <v>474926.9841269841</v>
+        <v>2019997.557377049</v>
       </c>
       <c r="O82" t="n">
-        <v>13497424.92512294</v>
+        <v>58014328.4608466</v>
       </c>
       <c r="P82" t="n">
-        <v>264405892.5099424</v>
+        <v>154071926.61</v>
       </c>
       <c r="Q82" t="n">
-        <v>9324087</v>
+        <v>5790001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TSLR</t>
+          <t>HOOG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5311,57 +5311,57 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.003261057880561902</v>
+        <v>0.004780964738307878</v>
       </c>
       <c r="E83" t="n">
-        <v>305724.1763026783</v>
+        <v>448215.4442163635</v>
       </c>
       <c r="F83" t="n">
-        <v>203782.1368553031</v>
+        <v>299158.0966219627</v>
       </c>
       <c r="G83" t="n">
-        <v>-101942.0394473752</v>
+        <v>-149057.3475944009</v>
       </c>
       <c r="H83" t="n">
-        <v>101942.0394473752</v>
+        <v>149057.3475944009</v>
       </c>
       <c r="I83" t="n">
-        <v>26.61000061035156</v>
+        <v>21.44860076904297</v>
       </c>
       <c r="J83" t="n">
-        <v>3830.967196886073</v>
+        <v>6949.513826073785</v>
       </c>
       <c r="K83" t="n">
-        <v>0.001975130986676388</v>
+        <v>0.00991352851291208</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0006616522665119882</v>
+        <v>0.002351324545135396</v>
       </c>
       <c r="M83" t="n">
-        <v>0.0006616522513357205</v>
+        <v>0.00193579772314033</v>
       </c>
       <c r="N83" t="n">
-        <v>1939601.587301587</v>
+        <v>701013.1475409836</v>
       </c>
       <c r="O83" t="n">
-        <v>51612799.4219341</v>
+        <v>15035751.13545677</v>
       </c>
       <c r="P83" t="n">
-        <v>154071926.61</v>
+        <v>63392928</v>
       </c>
       <c r="Q83" t="n">
-        <v>5790001</v>
+        <v>3590000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>LLYX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5370,46 +5370,46 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.003250701282584665</v>
+        <v>0.004689066246150323</v>
       </c>
       <c r="E84" t="n">
-        <v>304753.2452423123</v>
+        <v>439599.9605765928</v>
       </c>
       <c r="F84" t="n">
-        <v>202726.7151980163</v>
+        <v>292871.0017726566</v>
       </c>
       <c r="G84" t="n">
-        <v>-102026.5300442961</v>
+        <v>-146728.9588039362</v>
       </c>
       <c r="H84" t="n">
-        <v>102026.5300442961</v>
+        <v>146728.9588039362</v>
       </c>
       <c r="I84" t="n">
-        <v>61.63000106811523</v>
+        <v>18.52000045776367</v>
       </c>
       <c r="J84" t="n">
-        <v>1655.46857498077</v>
+        <v>7922.729761187813</v>
       </c>
       <c r="K84" t="n">
-        <v>0.003654929866648976</v>
+        <v>0.01831642584041338</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0005133234388677241</v>
+        <v>0.002532429389091063</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0005133234299712682</v>
+        <v>0.002441519186806722</v>
       </c>
       <c r="N84" t="n">
-        <v>452941.2698412698</v>
+        <v>432547.8032786885</v>
       </c>
       <c r="O84" t="n">
-        <v>27914770.94411093</v>
+        <v>8010785.514725982</v>
       </c>
       <c r="P84" t="n">
-        <v>198756811.63</v>
+        <v>57940000</v>
       </c>
       <c r="Q84" t="n">
-        <v>3225001</v>
+        <v>3245000</v>
       </c>
     </row>
     <row r="85">
@@ -5429,40 +5429,40 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.003211746563693998</v>
+        <v>0.004668391359909717</v>
       </c>
       <c r="E85" t="n">
-        <v>301101.2403463123</v>
+        <v>437661.689991536</v>
       </c>
       <c r="F85" t="n">
-        <v>200967.8049135513</v>
+        <v>292114.0711050924</v>
       </c>
       <c r="G85" t="n">
-        <v>-100133.435432761</v>
+        <v>-145547.6188864436</v>
       </c>
       <c r="H85" t="n">
-        <v>100133.435432761</v>
+        <v>145547.6188864436</v>
       </c>
       <c r="I85" t="n">
-        <v>20.79000091552734</v>
+        <v>21.70999908447266</v>
       </c>
       <c r="J85" t="n">
-        <v>4816.422848638489</v>
+        <v>6704.174344739684</v>
       </c>
       <c r="K85" t="n">
-        <v>0.05070427101534403</v>
+        <v>0.07319515187246821</v>
       </c>
       <c r="L85" t="n">
-        <v>0.002432016987656012</v>
+        <v>0.003535025839420096</v>
       </c>
       <c r="M85" t="n">
-        <v>0.00244488469474035</v>
+        <v>0.003403134185147048</v>
       </c>
       <c r="N85" t="n">
-        <v>94990.47619047618</v>
+        <v>91593.14754098361</v>
       </c>
       <c r="O85" t="n">
-        <v>1974852.086966378</v>
+        <v>1988487.149258723</v>
       </c>
       <c r="P85" t="n">
         <v>41173000</v>
@@ -5474,12 +5474,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LLYX</t>
+          <t>CRMG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5488,57 +5488,57 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.003009720890632562</v>
+        <v>0.004456375730927578</v>
       </c>
       <c r="E86" t="n">
-        <v>282161.3334968027</v>
+        <v>417785.2247744605</v>
       </c>
       <c r="F86" t="n">
-        <v>187981.9831974694</v>
+        <v>277776.7714318129</v>
       </c>
       <c r="G86" t="n">
-        <v>-94179.35029933334</v>
+        <v>-140008.4533426476</v>
       </c>
       <c r="H86" t="n">
-        <v>94179.35029933334</v>
+        <v>140008.4533426476</v>
       </c>
       <c r="I86" t="n">
-        <v>17.80999946594238</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="J86" t="n">
-        <v>5288.004105751387</v>
+        <v>25409.88158380895</v>
       </c>
       <c r="K86" t="n">
-        <v>0.01242296838781426</v>
+        <v>0.01976500240517137</v>
       </c>
       <c r="L86" t="n">
-        <v>0.001625463415590841</v>
+        <v>0.004569703330010957</v>
       </c>
       <c r="M86" t="n">
-        <v>0.001629585240601352</v>
+        <v>0.004557826293059901</v>
       </c>
       <c r="N86" t="n">
-        <v>425663.4920634921</v>
+        <v>1285599.721311475</v>
       </c>
       <c r="O86" t="n">
-        <v>7581066.566321963</v>
+        <v>7083654.758676654</v>
       </c>
       <c r="P86" t="n">
-        <v>57940000</v>
+        <v>30638412</v>
       </c>
       <c r="Q86" t="n">
-        <v>3245000</v>
+        <v>5575000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CRMG</t>
+          <t>JOBX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>JOBY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5547,46 +5547,46 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.002968755932192689</v>
+        <v>0.004422978372581879</v>
       </c>
       <c r="E87" t="n">
-        <v>278320.8686430646</v>
+        <v>414654.2224295511</v>
       </c>
       <c r="F87" t="n">
-        <v>185049.8000629491</v>
+        <v>275881.0556191257</v>
       </c>
       <c r="G87" t="n">
-        <v>-93271.06858011549</v>
+        <v>-138773.1668104254</v>
       </c>
       <c r="H87" t="n">
-        <v>93271.06858011549</v>
+        <v>138773.1668104254</v>
       </c>
       <c r="I87" t="n">
-        <v>5.789999961853027</v>
+        <v>28.95999908447266</v>
       </c>
       <c r="J87" t="n">
-        <v>16108.99295243952</v>
+        <v>4791.891270633042</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01251751827000802</v>
+        <v>0.06198960882128288</v>
       </c>
       <c r="L87" t="n">
-        <v>0.003044252704093002</v>
+        <v>0.003676953641404948</v>
       </c>
       <c r="M87" t="n">
-        <v>0.00288950546232099</v>
+        <v>0.003729150502211737</v>
       </c>
       <c r="N87" t="n">
-        <v>1286915.873015873</v>
+        <v>77301.52459016393</v>
       </c>
       <c r="O87" t="n">
-        <v>7451242.855669959</v>
+        <v>2238652.081359488</v>
       </c>
       <c r="P87" t="n">
-        <v>30638412</v>
+        <v>37741342.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>5575000</v>
+        <v>1284982</v>
       </c>
     </row>
     <row r="88">
@@ -5606,40 +5606,40 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.002923640973182075</v>
+        <v>0.00440387927317602</v>
       </c>
       <c r="E88" t="n">
-        <v>274091.3412358195</v>
+        <v>412863.6818602519</v>
       </c>
       <c r="F88" t="n">
-        <v>182237.6746018317</v>
+        <v>274504.5391456903</v>
       </c>
       <c r="G88" t="n">
-        <v>-91853.66663398777</v>
+        <v>-138359.1427145617</v>
       </c>
       <c r="H88" t="n">
-        <v>91853.66663398777</v>
+        <v>138359.1427145617</v>
       </c>
       <c r="I88" t="n">
-        <v>40.52999877929688</v>
+        <v>44.22000122070312</v>
       </c>
       <c r="J88" t="n">
-        <v>2266.31308661444</v>
+        <v>3128.881476597157</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0003749275321298024</v>
+        <v>0.0005375227718383177</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0002049252986948392</v>
+        <v>0.0003086788985890316</v>
       </c>
       <c r="M88" t="n">
-        <v>0.0002053663612707576</v>
+        <v>0.0002835296709406289</v>
       </c>
       <c r="N88" t="n">
-        <v>6044669.682539683</v>
+        <v>5820928.229508197</v>
       </c>
       <c r="O88" t="n">
-        <v>244990454.8545862</v>
+        <v>257401453.4144777</v>
       </c>
       <c r="P88" t="n">
         <v>448230000</v>
@@ -5651,12 +5651,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JOBX</t>
+          <t>MEXX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JOBY</t>
+          <t>EWW</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5665,57 +5665,57 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.002831130159700393</v>
+        <v>0.004177103617314624</v>
       </c>
       <c r="E89" t="n">
-        <v>265418.4524719118</v>
+        <v>391603.4641232461</v>
       </c>
       <c r="F89" t="n">
-        <v>176590.3224612318</v>
+        <v>292663.7308935225</v>
       </c>
       <c r="G89" t="n">
-        <v>-88828.13001067998</v>
+        <v>-98939.73322972363</v>
       </c>
       <c r="H89" t="n">
-        <v>88828.13001067998</v>
+        <v>98939.73322972363</v>
       </c>
       <c r="I89" t="n">
-        <v>29.35000038146973</v>
+        <v>34.29000091552734</v>
       </c>
       <c r="J89" t="n">
-        <v>3026.512056427845</v>
+        <v>2885.381469468591</v>
       </c>
       <c r="K89" t="n">
-        <v>0.04006435241010994</v>
+        <v>0.05848560296241714</v>
       </c>
       <c r="L89" t="n">
-        <v>0.002353602815363759</v>
+        <v>0.004119904221459175</v>
       </c>
       <c r="M89" t="n">
-        <v>0.002355295293185309</v>
+        <v>0.004029721684953166</v>
       </c>
       <c r="N89" t="n">
-        <v>75541.26984126984</v>
+        <v>49334.90163934427</v>
       </c>
       <c r="O89" t="n">
-        <v>2217136.298657977</v>
+        <v>1691693.822380566</v>
       </c>
       <c r="P89" t="n">
-        <v>37741342.52</v>
+        <v>24015056.64000156</v>
       </c>
       <c r="Q89" t="n">
-        <v>1284982</v>
+        <v>716025</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BITU</t>
+          <t>TSMG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IBIT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5724,57 +5724,57 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.002618157249644981</v>
+        <v>0.004026847425917149</v>
       </c>
       <c r="E90" t="n">
-        <v>245452.2421542169</v>
+        <v>377516.9461797327</v>
       </c>
       <c r="F90" t="n">
-        <v>163416.0649636364</v>
+        <v>250790.8816682414</v>
       </c>
       <c r="G90" t="n">
-        <v>-82036.17719058054</v>
+        <v>-126726.0645114913</v>
       </c>
       <c r="H90" t="n">
-        <v>82036.17719058054</v>
+        <v>126726.0645114913</v>
       </c>
       <c r="I90" t="n">
-        <v>15.85000038146973</v>
+        <v>38.27999877929688</v>
       </c>
       <c r="J90" t="n">
-        <v>5175.783925310767</v>
+        <v>3310.503358219257</v>
       </c>
       <c r="K90" t="n">
-        <v>0.001043631403369067</v>
+        <v>0.02905263406388229</v>
       </c>
       <c r="L90" t="n">
-        <v>0.000147840364692348</v>
+        <v>0.00551594727645253</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0001478795407231648</v>
+        <v>0.00533952154551493</v>
       </c>
       <c r="N90" t="n">
-        <v>4959398.412698412</v>
+        <v>113948.4754098361</v>
       </c>
       <c r="O90" t="n">
-        <v>78606466.73313019</v>
+        <v>4361947.499591265</v>
       </c>
       <c r="P90" t="n">
-        <v>554897015.8542</v>
+        <v>22974488</v>
       </c>
       <c r="Q90" t="n">
-        <v>35000000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ARMG</t>
+          <t>BITU</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>IBIT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5783,46 +5783,46 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.002584101146256768</v>
+        <v>0.003793386839172323</v>
       </c>
       <c r="E91" t="n">
-        <v>242259.482461572</v>
+        <v>355630.0161724053</v>
       </c>
       <c r="F91" t="n">
-        <v>161425.4876462326</v>
+        <v>236769.7166495426</v>
       </c>
       <c r="G91" t="n">
-        <v>-80833.99481533932</v>
+        <v>-118860.2995228628</v>
       </c>
       <c r="H91" t="n">
-        <v>80833.99481533932</v>
+        <v>118860.2995228628</v>
       </c>
       <c r="I91" t="n">
-        <v>17.46999931335449</v>
+        <v>16.54000091552734</v>
       </c>
       <c r="J91" t="n">
-        <v>4627.017629791653</v>
+        <v>7186.232947017533</v>
       </c>
       <c r="K91" t="n">
-        <v>0.003083145003827453</v>
+        <v>0.001470553325240383</v>
       </c>
       <c r="L91" t="n">
-        <v>0.00126882812749718</v>
+        <v>0.0002142024486109211</v>
       </c>
       <c r="M91" t="n">
-        <v>0.001274660504074836</v>
+        <v>0.0002053209413433581</v>
       </c>
       <c r="N91" t="n">
-        <v>1500746.031746032</v>
+        <v>4886754.409836066</v>
       </c>
       <c r="O91" t="n">
-        <v>26218032.14412265</v>
+        <v>80826922.41264582</v>
       </c>
       <c r="P91" t="n">
-        <v>63707600</v>
+        <v>554897015.8542</v>
       </c>
       <c r="Q91" t="n">
-        <v>3630000</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="92">
@@ -5842,40 +5842,40 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.002450729345253013</v>
+        <v>0.003669540188203093</v>
       </c>
       <c r="E92" t="n">
-        <v>229755.87611747</v>
+        <v>344019.3926440399</v>
       </c>
       <c r="F92" t="n">
-        <v>153323.4489326829</v>
+        <v>229575.1502474864</v>
       </c>
       <c r="G92" t="n">
-        <v>-76432.4271847871</v>
+        <v>-114444.2423965536</v>
       </c>
       <c r="H92" t="n">
-        <v>76432.4271847871</v>
+        <v>114444.2423965536</v>
       </c>
       <c r="I92" t="n">
-        <v>16.20000076293945</v>
+        <v>15.81999969482422</v>
       </c>
       <c r="J92" t="n">
-        <v>4718.05083859259</v>
+        <v>7234.149469294613</v>
       </c>
       <c r="K92" t="n">
-        <v>0.00379349727432452</v>
+        <v>0.0058053024610145</v>
       </c>
       <c r="L92" t="n">
-        <v>0.001116698211619199</v>
+        <v>0.0016720610023985</v>
       </c>
       <c r="M92" t="n">
-        <v>0.001116698159028268</v>
+        <v>0.001712224321200069</v>
       </c>
       <c r="N92" t="n">
-        <v>1243720.634920635</v>
+        <v>1246127.918032787</v>
       </c>
       <c r="O92" t="n">
-        <v>20148275.23459783</v>
+        <v>19713743.28299063</v>
       </c>
       <c r="P92" t="n">
         <v>68445016.2</v>
@@ -5887,12 +5887,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMZZ</t>
+          <t>ARMG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5901,57 +5901,57 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.002449405470207858</v>
+        <v>0.003628408114126558</v>
       </c>
       <c r="E93" t="n">
-        <v>229631.7628319867</v>
+        <v>340163.2606993648</v>
       </c>
       <c r="F93" t="n">
-        <v>152883.1789977665</v>
+        <v>226662.0058780886</v>
       </c>
       <c r="G93" t="n">
-        <v>-76748.58383422016</v>
+        <v>-113501.2548212762</v>
       </c>
       <c r="H93" t="n">
-        <v>76748.58383422016</v>
+        <v>113501.2548212762</v>
       </c>
       <c r="I93" t="n">
-        <v>41.36999893188477</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="J93" t="n">
-        <v>1855.174904901154</v>
+        <v>6534.326386727189</v>
       </c>
       <c r="K93" t="n">
-        <v>0.006886280528200226</v>
+        <v>0.004291223932829009</v>
       </c>
       <c r="L93" t="n">
-        <v>0.001152282519877731</v>
+        <v>0.001781596776856705</v>
       </c>
       <c r="M93" t="n">
-        <v>0.001152282549628046</v>
+        <v>0.00180008991369895</v>
       </c>
       <c r="N93" t="n">
-        <v>269401.5873015873</v>
+        <v>1522718.573770492</v>
       </c>
       <c r="O93" t="n">
-        <v>11145143.37891473</v>
+        <v>26449622.90430973</v>
       </c>
       <c r="P93" t="n">
-        <v>66605699.99999999</v>
+        <v>63707600</v>
       </c>
       <c r="Q93" t="n">
-        <v>1610000</v>
+        <v>3630000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NOWL</t>
+          <t>AMZZ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5960,57 +5960,57 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.002410746495144662</v>
+        <v>0.0036209236668666</v>
       </c>
       <c r="E94" t="n">
-        <v>226007.4839198121</v>
+        <v>339461.5937687437</v>
       </c>
       <c r="F94" t="n">
-        <v>150571.0740667373</v>
+        <v>226005.1787390834</v>
       </c>
       <c r="G94" t="n">
-        <v>-75436.40985307479</v>
+        <v>-113456.4150296603</v>
       </c>
       <c r="H94" t="n">
-        <v>75436.40985307479</v>
+        <v>113456.4150296603</v>
       </c>
       <c r="I94" t="n">
-        <v>4.079999923706055</v>
+        <v>40.18000030517578</v>
       </c>
       <c r="J94" t="n">
-        <v>18489.31648620041</v>
+        <v>2823.703687604141</v>
       </c>
       <c r="K94" t="n">
-        <v>0.004003782808847943</v>
+        <v>0.01109015378005503</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0006738088726913497</v>
+        <v>0.00170340398839229</v>
       </c>
       <c r="M94" t="n">
-        <v>0.0006738088852912364</v>
+        <v>0.001753853222114373</v>
       </c>
       <c r="N94" t="n">
-        <v>4617961.904761905</v>
+        <v>254613.5737704918</v>
       </c>
       <c r="O94" t="n">
-        <v>18841284.21910604</v>
+        <v>10230373.47180026</v>
       </c>
       <c r="P94" t="n">
-        <v>111955204.08</v>
+        <v>66605699.99999999</v>
       </c>
       <c r="Q94" t="n">
-        <v>27440001</v>
+        <v>1610000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>UNHG</t>
+          <t>GOOX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6019,57 +6019,57 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.002368810145483444</v>
+        <v>0.003589510431227271</v>
       </c>
       <c r="E95" t="n">
-        <v>222075.9511390728</v>
+        <v>336516.6029275566</v>
       </c>
       <c r="F95" t="n">
-        <v>147951.8018937214</v>
+        <v>223742.9424290457</v>
       </c>
       <c r="G95" t="n">
-        <v>-74124.14924535141</v>
+        <v>-112773.6604985109</v>
       </c>
       <c r="H95" t="n">
-        <v>74124.14924535141</v>
+        <v>112773.6604985109</v>
       </c>
       <c r="I95" t="n">
-        <v>19.48999977111816</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="J95" t="n">
-        <v>3803.188820719972</v>
+        <v>1141.202801525788</v>
       </c>
       <c r="K95" t="n">
-        <v>0.002120776680265416</v>
+        <v>0.01373950731085074</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0004024538387361931</v>
+        <v>0.002051687315655428</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0004024538434624309</v>
+        <v>0.002153212833067525</v>
       </c>
       <c r="N95" t="n">
-        <v>1793300</v>
+        <v>83059.95081967213</v>
       </c>
       <c r="O95" t="n">
-        <v>34951416.5895462</v>
+        <v>8207984.314652114</v>
       </c>
       <c r="P95" t="n">
-        <v>184180500</v>
+        <v>54966300</v>
       </c>
       <c r="Q95" t="n">
-        <v>9450000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TSLT</t>
+          <t>NOWL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6078,57 +6078,57 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.002272533508491805</v>
+        <v>0.003421450392877994</v>
       </c>
       <c r="E96" t="n">
-        <v>213050.0164211067</v>
+        <v>320760.9743323119</v>
       </c>
       <c r="F96" t="n">
-        <v>141867.2511617994</v>
+        <v>213697.8987874815</v>
       </c>
       <c r="G96" t="n">
-        <v>-71182.76525930729</v>
+        <v>-107063.0755448304</v>
       </c>
       <c r="H96" t="n">
-        <v>71182.76525930729</v>
+        <v>107063.0755448304</v>
       </c>
       <c r="I96" t="n">
-        <v>21.79000091552734</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="J96" t="n">
-        <v>3266.762839306864</v>
+        <v>25986.18410648378</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0009775287057546271</v>
+        <v>0.005206501338059683</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0002855672018041116</v>
+        <v>0.0009563028036492718</v>
       </c>
       <c r="M96" t="n">
-        <v>0.0002647295655840247</v>
+        <v>0.0009470183367152128</v>
       </c>
       <c r="N96" t="n">
-        <v>3341858.73015873</v>
+        <v>4991102.934426229</v>
       </c>
       <c r="O96" t="n">
-        <v>72819104.78972177</v>
+        <v>20563343.51864966</v>
       </c>
       <c r="P96" t="n">
-        <v>249268000</v>
+        <v>111955204.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>12340000</v>
+        <v>27440001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GOOX</t>
+          <t>TSLT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6137,57 +6137,57 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.002268258692096247</v>
+        <v>0.003354526180610054</v>
       </c>
       <c r="E97" t="n">
-        <v>212649.2523840232</v>
+        <v>314486.8294321925</v>
       </c>
       <c r="F97" t="n">
-        <v>141386.0980998331</v>
+        <v>209412.7133506047</v>
       </c>
       <c r="G97" t="n">
-        <v>-71263.15428419008</v>
+        <v>-105074.1160815879</v>
       </c>
       <c r="H97" t="n">
-        <v>71263.15428419008</v>
+        <v>105074.1160815879</v>
       </c>
       <c r="I97" t="n">
-        <v>104.2300033569336</v>
+        <v>23.48999977111816</v>
       </c>
       <c r="J97" t="n">
-        <v>683.7105630722357</v>
+        <v>4473.142490651722</v>
       </c>
       <c r="K97" t="n">
-        <v>0.007833872667239715</v>
+        <v>0.001310576834284327</v>
       </c>
       <c r="L97" t="n">
-        <v>0.001296488107880466</v>
+        <v>0.0004215307062342053</v>
       </c>
       <c r="M97" t="n">
-        <v>0.001290019930324973</v>
+        <v>0.0003624912877351477</v>
       </c>
       <c r="N97" t="n">
-        <v>87276.19047619047</v>
+        <v>3413109.68852459</v>
       </c>
       <c r="O97" t="n">
-        <v>9096797.626313709</v>
+        <v>80173945.80224381</v>
       </c>
       <c r="P97" t="n">
-        <v>54966300</v>
+        <v>249268000</v>
       </c>
       <c r="Q97" t="n">
-        <v>530000</v>
+        <v>12340000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TSMU</t>
+          <t>SPXL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6196,57 +6196,57 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.002073035345282641</v>
+        <v>0.003303951441196892</v>
       </c>
       <c r="E98" t="n">
-        <v>194347.0636202476</v>
+        <v>309745.4476122086</v>
       </c>
       <c r="F98" t="n">
-        <v>129348.0456870544</v>
+        <v>232134.4609892548</v>
       </c>
       <c r="G98" t="n">
-        <v>-64999.01793319318</v>
+        <v>-77610.98662295379</v>
       </c>
       <c r="H98" t="n">
-        <v>64999.01793319318</v>
+        <v>77610.98662295379</v>
       </c>
       <c r="I98" t="n">
-        <v>71.90000152587891</v>
+        <v>267.2699890136719</v>
       </c>
       <c r="J98" t="n">
-        <v>904.019701721399</v>
+        <v>290.3842175074273</v>
       </c>
       <c r="K98" t="n">
-        <v>0.009113247653163955</v>
+        <v>8.902418039668826e-05</v>
       </c>
       <c r="L98" t="n">
-        <v>0.001397616986893362</v>
+        <v>1.24450073046026e-05</v>
       </c>
       <c r="M98" t="n">
-        <v>0.001397617765624916</v>
+        <v>1.207418733610145e-05</v>
       </c>
       <c r="N98" t="n">
-        <v>99198.41269841269</v>
+        <v>3261857.803278688</v>
       </c>
       <c r="O98" t="n">
-        <v>7132366.024380638</v>
+        <v>871796699.246455</v>
       </c>
       <c r="P98" t="n">
-        <v>46507032</v>
+        <v>6236315071.848172</v>
       </c>
       <c r="Q98" t="n">
-        <v>646829</v>
+        <v>24050001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NFLU</t>
+          <t>UNHG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6255,46 +6255,46 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.002070623555476362</v>
+        <v>0.003228337873836997</v>
       </c>
       <c r="E99" t="n">
-        <v>194120.958325909</v>
+        <v>302656.6756722184</v>
       </c>
       <c r="F99" t="n">
-        <v>129197.5608924946</v>
+        <v>201636.4234451762</v>
       </c>
       <c r="G99" t="n">
-        <v>-64923.39743341436</v>
+        <v>-101020.2522270422</v>
       </c>
       <c r="H99" t="n">
-        <v>64923.39743341436</v>
+        <v>101020.2522270422</v>
       </c>
       <c r="I99" t="n">
-        <v>25.60000038146973</v>
+        <v>19.95999908447266</v>
       </c>
       <c r="J99" t="n">
-        <v>2536.070174452358</v>
+        <v>5061.135113259007</v>
       </c>
       <c r="K99" t="n">
-        <v>0.009314166680686882</v>
+        <v>0.002912030330283789</v>
       </c>
       <c r="L99" t="n">
-        <v>0.002047927494587546</v>
+        <v>0.0005484850580112563</v>
       </c>
       <c r="M99" t="n">
-        <v>0.002095925764010213</v>
+        <v>0.0005355698532549214</v>
       </c>
       <c r="N99" t="n">
-        <v>272280.9523809524</v>
+        <v>1738009.065573771</v>
       </c>
       <c r="O99" t="n">
-        <v>6970392.484819321</v>
+        <v>34690659.35765763</v>
       </c>
       <c r="P99" t="n">
-        <v>31702000</v>
+        <v>184180500</v>
       </c>
       <c r="Q99" t="n">
-        <v>1210000</v>
+        <v>9450000</v>
       </c>
     </row>
     <row r="100">
@@ -6314,40 +6314,40 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.002064111817454452</v>
+        <v>0.003130076345010392</v>
       </c>
       <c r="E100" t="n">
-        <v>193510.4828863549</v>
+        <v>293444.6573447242</v>
       </c>
       <c r="F100" t="n">
-        <v>128704.5609552247</v>
+        <v>195171.1619178239</v>
       </c>
       <c r="G100" t="n">
-        <v>-64805.92193113024</v>
+        <v>-98273.49542690028</v>
       </c>
       <c r="H100" t="n">
-        <v>64805.92193113024</v>
+        <v>98273.49542690028</v>
       </c>
       <c r="I100" t="n">
-        <v>143.6699981689453</v>
+        <v>149.1999969482422</v>
       </c>
       <c r="J100" t="n">
-        <v>451.0748434403351</v>
+        <v>658.6695538672938</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0009198785202017652</v>
+        <v>0.001323089863601738</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0001019709035863196</v>
+        <v>0.0001546315032431218</v>
       </c>
       <c r="M100" t="n">
-        <v>9.859557264366393e-05</v>
+        <v>0.0001439714557149373</v>
       </c>
       <c r="N100" t="n">
-        <v>490363.4920634921</v>
+        <v>497826.7704918033</v>
       </c>
       <c r="O100" t="n">
-        <v>70450522.00687954</v>
+        <v>74275752.63813032</v>
       </c>
       <c r="P100" t="n">
         <v>635533467.4098603</v>
@@ -6359,12 +6359,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LINT</t>
+          <t>BMNG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6373,57 +6373,57 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.001821317795992912</v>
+        <v>0.002966271947970803</v>
       </c>
       <c r="E101" t="n">
-        <v>170748.5433743355</v>
+        <v>278087.9951222628</v>
       </c>
       <c r="F101" t="n">
-        <v>113584.6520538348</v>
+        <v>185175.2002267523</v>
       </c>
       <c r="G101" t="n">
-        <v>-57163.89132050065</v>
+        <v>-92912.79489551045</v>
       </c>
       <c r="H101" t="n">
-        <v>57163.89132050065</v>
+        <v>92912.79489551045</v>
       </c>
       <c r="I101" t="n">
-        <v>230.7400054931641</v>
+        <v>30.97999954223633</v>
       </c>
       <c r="J101" t="n">
-        <v>247.7415704239211</v>
+        <v>2999.121893750791</v>
       </c>
       <c r="K101" t="n">
-        <v>0.001734730686958946</v>
+        <v>0.001217181551383622</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0007622794278227972</v>
+        <v>0.002426405298338605</v>
       </c>
       <c r="M101" t="n">
-        <v>0.0007622794096754198</v>
+        <v>0.002253315141565244</v>
       </c>
       <c r="N101" t="n">
-        <v>142812.6984126984</v>
+        <v>2463988.950819672</v>
       </c>
       <c r="O101" t="n">
-        <v>32952602.81623961</v>
+        <v>76334376.56846881</v>
       </c>
       <c r="P101" t="n">
-        <v>74990730.74000001</v>
+        <v>38292364</v>
       </c>
       <c r="Q101" t="n">
-        <v>325001</v>
+        <v>1330982</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NVDL</t>
+          <t>TSMU</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6432,57 +6432,57 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.001789875070730042</v>
+        <v>0.002891844035116449</v>
       </c>
       <c r="E102" t="n">
-        <v>167800.7878809414</v>
+        <v>271110.378292167</v>
       </c>
       <c r="F102" t="n">
-        <v>111642.5590051243</v>
+        <v>180438.010970372</v>
       </c>
       <c r="G102" t="n">
-        <v>-56158.22887581707</v>
+        <v>-90672.36732179498</v>
       </c>
       <c r="H102" t="n">
-        <v>56158.22887581707</v>
+        <v>90672.36732179498</v>
       </c>
       <c r="I102" t="n">
-        <v>107.870002746582</v>
+        <v>69.61000061035156</v>
       </c>
       <c r="J102" t="n">
-        <v>520.6102479458451</v>
+        <v>1302.576735049063</v>
       </c>
       <c r="K102" t="n">
-        <v>5.632680579003161e-05</v>
+        <v>0.01288289394469414</v>
       </c>
       <c r="L102" t="n">
-        <v>1.333530177227955e-05</v>
+        <v>0.001949648546090728</v>
       </c>
       <c r="M102" t="n">
-        <v>1.333530143273659e-05</v>
+        <v>0.002013788397009198</v>
       </c>
       <c r="N102" t="n">
-        <v>9242673.015873017</v>
+        <v>101109.0163934426</v>
       </c>
       <c r="O102" t="n">
-        <v>997007163.6079819</v>
+        <v>7038198.692859587</v>
       </c>
       <c r="P102" t="n">
-        <v>4211245447.22</v>
+        <v>46507032</v>
       </c>
       <c r="Q102" t="n">
-        <v>39040006</v>
+        <v>646829</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AVGX</t>
+          <t>NVDL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6491,57 +6491,57 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.00174628759869851</v>
+        <v>0.00269617788678112</v>
       </c>
       <c r="E103" t="n">
-        <v>163714.4623779853</v>
+        <v>252766.6768857299</v>
       </c>
       <c r="F103" t="n">
-        <v>108997.0618505838</v>
+        <v>168172.7421850171</v>
       </c>
       <c r="G103" t="n">
-        <v>-54717.4005274015</v>
+        <v>-84593.93470071284</v>
       </c>
       <c r="H103" t="n">
-        <v>54717.4005274015</v>
+        <v>84593.93470071284</v>
       </c>
       <c r="I103" t="n">
-        <v>65.30000305175781</v>
+        <v>112.1399993896484</v>
       </c>
       <c r="J103" t="n">
-        <v>837.9387131732847</v>
+        <v>754.3600424570864</v>
       </c>
       <c r="K103" t="n">
-        <v>0.001210880206666061</v>
+        <v>8.263412956761241e-05</v>
       </c>
       <c r="L103" t="n">
-        <v>0.0002910190433326322</v>
+        <v>2.008762865070153e-05</v>
       </c>
       <c r="M103" t="n">
-        <v>0.0002909509420740572</v>
+        <v>1.932274401948315e-05</v>
       </c>
       <c r="N103" t="n">
-        <v>692007.9365079365</v>
+        <v>9128916.180327868</v>
       </c>
       <c r="O103" t="n">
-        <v>45188120.36580887</v>
+        <v>1023716654.890119</v>
       </c>
       <c r="P103" t="n">
-        <v>188020000</v>
+        <v>4211245447.22</v>
       </c>
       <c r="Q103" t="n">
-        <v>2880000</v>
+        <v>39040006</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PLTG</t>
+          <t>AVGX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6550,57 +6550,57 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.001592189534945935</v>
+        <v>0.002678202603457949</v>
       </c>
       <c r="E104" t="n">
-        <v>149267.7689011814</v>
+        <v>251081.4940741827</v>
       </c>
       <c r="F104" t="n">
-        <v>99445.41613042659</v>
+        <v>167163.882418373</v>
       </c>
       <c r="G104" t="n">
-        <v>-49822.3527707548</v>
+        <v>-83917.61165580973</v>
       </c>
       <c r="H104" t="n">
-        <v>49822.3527707548</v>
+        <v>83917.61165580973</v>
       </c>
       <c r="I104" t="n">
-        <v>13.38000011444092</v>
+        <v>64.73000335693359</v>
       </c>
       <c r="J104" t="n">
-        <v>3723.643672990852</v>
+        <v>1296.42526346047</v>
       </c>
       <c r="K104" t="n">
-        <v>0.01153505423086004</v>
+        <v>0.00191596288790273</v>
       </c>
       <c r="L104" t="n">
-        <v>0.001944838246859707</v>
+        <v>0.0004463227936166883</v>
       </c>
       <c r="M104" t="n">
-        <v>0.001944838228706894</v>
+        <v>0.0004501476609237742</v>
       </c>
       <c r="N104" t="n">
-        <v>322811.1111111111</v>
+        <v>676644.2459016393</v>
       </c>
       <c r="O104" t="n">
-        <v>4319212.703609467</v>
+        <v>43799184.30866291</v>
       </c>
       <c r="P104" t="n">
-        <v>25617736</v>
+        <v>188020000</v>
       </c>
       <c r="Q104" t="n">
-        <v>1914629</v>
+        <v>2880000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NFXL</t>
+          <t>LINT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6609,46 +6609,46 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.001573733113400512</v>
+        <v>0.002439589183609461</v>
       </c>
       <c r="E105" t="n">
-        <v>147537.479381298</v>
+        <v>228711.485963387</v>
       </c>
       <c r="F105" t="n">
-        <v>98374.70717826636</v>
+        <v>152142.52514538</v>
       </c>
       <c r="G105" t="n">
-        <v>-49162.77220303167</v>
+        <v>-76568.96081800704</v>
       </c>
       <c r="H105" t="n">
-        <v>49162.77220303167</v>
+        <v>76568.96081800704</v>
       </c>
       <c r="I105" t="n">
-        <v>24.22999954223633</v>
+        <v>247.5</v>
       </c>
       <c r="J105" t="n">
-        <v>2029.004256369629</v>
+        <v>309.3695386586143</v>
       </c>
       <c r="K105" t="n">
-        <v>0.002118481517809954</v>
+        <v>0.002096427084533151</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0002790780437763592</v>
+        <v>0.001021045668743766</v>
       </c>
       <c r="M105" t="n">
-        <v>0.0002790780425693706</v>
+        <v>0.0009519033438623705</v>
       </c>
       <c r="N105" t="n">
-        <v>957763.4920634921</v>
+        <v>147569.9016393443</v>
       </c>
       <c r="O105" t="n">
-        <v>23206608.97426908</v>
+        <v>36523550.65573771</v>
       </c>
       <c r="P105" t="n">
-        <v>176161376</v>
+        <v>74990730.74000001</v>
       </c>
       <c r="Q105" t="n">
-        <v>7270383</v>
+        <v>325001</v>
       </c>
     </row>
     <row r="106">
@@ -6668,40 +6668,40 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.001472707153627277</v>
+        <v>0.002314135104545098</v>
       </c>
       <c r="E106" t="n">
-        <v>138066.2956525572</v>
+        <v>216950.166051103</v>
       </c>
       <c r="F106" t="n">
-        <v>92028.85128691625</v>
+        <v>144609.3304221923</v>
       </c>
       <c r="G106" t="n">
-        <v>-46037.44436564094</v>
+        <v>-72340.83562891062</v>
       </c>
       <c r="H106" t="n">
-        <v>46037.44436564094</v>
+        <v>72340.83562891062</v>
       </c>
       <c r="I106" t="n">
-        <v>24.69000053405762</v>
+        <v>23.81999969482422</v>
       </c>
       <c r="J106" t="n">
-        <v>1864.619010523571</v>
+        <v>3036.978864639925</v>
       </c>
       <c r="K106" t="n">
-        <v>0.0005044481742110735</v>
+        <v>0.0008140341092628479</v>
       </c>
       <c r="L106" t="n">
-        <v>8.570127040437983e-05</v>
+        <v>0.0001346665003007656</v>
       </c>
       <c r="M106" t="n">
-        <v>8.785012592101035e-05</v>
+        <v>0.0001430849809919879</v>
       </c>
       <c r="N106" t="n">
-        <v>3696353.968253968</v>
+        <v>3730775.934426229</v>
       </c>
       <c r="O106" t="n">
-        <v>91262981.45025647</v>
+        <v>88867081.61949033</v>
       </c>
       <c r="P106" t="n">
         <v>537185086.6202347</v>
@@ -6713,12 +6713,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TARK</t>
+          <t>PLTG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6727,57 +6727,57 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.001317454693527656</v>
+        <v>0.002165421394977922</v>
       </c>
       <c r="E107" t="n">
-        <v>123511.3775182177</v>
+        <v>203008.2557791802</v>
       </c>
       <c r="F107" t="n">
-        <v>82036.77123271815</v>
+        <v>135248.4908328584</v>
       </c>
       <c r="G107" t="n">
-        <v>-41474.60628549957</v>
+        <v>-67759.76494632184</v>
       </c>
       <c r="H107" t="n">
-        <v>41474.60628549957</v>
+        <v>67759.76494632184</v>
       </c>
       <c r="I107" t="n">
-        <v>47.25799942016602</v>
+        <v>13.18000030517578</v>
       </c>
       <c r="J107" t="n">
-        <v>877.6208640732568</v>
+        <v>5141.104960347581</v>
       </c>
       <c r="K107" t="n">
-        <v>0.03787253540421617</v>
+        <v>0.01586345422007759</v>
       </c>
       <c r="L107" t="n">
-        <v>0.001696433646416488</v>
+        <v>0.00264503330607833</v>
       </c>
       <c r="M107" t="n">
-        <v>0.001699564011141518</v>
+        <v>0.002685170317773094</v>
       </c>
       <c r="N107" t="n">
-        <v>23173.01587301587</v>
+        <v>324084.8360655738</v>
       </c>
       <c r="O107" t="n">
-        <v>1095110.370690482</v>
+        <v>4271438.238247106</v>
       </c>
       <c r="P107" t="n">
-        <v>24448115.83</v>
+        <v>25617736</v>
       </c>
       <c r="Q107" t="n">
-        <v>516380</v>
+        <v>1914629</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TSMG</t>
+          <t>VRTL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6786,46 +6786,46 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.001258647379394532</v>
+        <v>0.001979093701757812</v>
       </c>
       <c r="E108" t="n">
-        <v>117998.1918182373</v>
+        <v>185540.0345397949</v>
       </c>
       <c r="F108" t="n">
-        <v>78388.19120788576</v>
+        <v>123320.0363708496</v>
       </c>
       <c r="G108" t="n">
-        <v>-39610.00061035157</v>
+        <v>-62219.99816894532</v>
       </c>
       <c r="H108" t="n">
-        <v>39610.00061035157</v>
+        <v>62219.99816894532</v>
       </c>
       <c r="I108" t="n">
-        <v>39.61000061035156</v>
+        <v>207.3999938964844</v>
       </c>
       <c r="J108" t="n">
-        <v>1000</v>
+        <v>300.0000000000001</v>
       </c>
       <c r="K108" t="n">
-        <v>0.008667895765113785</v>
+        <v>0.003654871484333185</v>
       </c>
       <c r="L108" t="n">
-        <v>0.001724086326117543</v>
+        <v>0.0009757811513977245</v>
       </c>
       <c r="M108" t="n">
-        <v>0.001612903225806452</v>
+        <v>0.0007894716066536669</v>
       </c>
       <c r="N108" t="n">
-        <v>115368.253968254</v>
+        <v>82082.22950819672</v>
       </c>
       <c r="O108" t="n">
-        <v>4569736.610097733</v>
+        <v>17023853.89900983</v>
       </c>
       <c r="P108" t="n">
-        <v>22974488</v>
+        <v>63764296</v>
       </c>
       <c r="Q108" t="n">
-        <v>620000</v>
+        <v>380001</v>
       </c>
     </row>
     <row r="109">
@@ -6845,40 +6845,40 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.001239559043750106</v>
+        <v>0.001813169297980022</v>
       </c>
       <c r="E109" t="n">
-        <v>116208.6603515724</v>
+        <v>169984.621685627</v>
       </c>
       <c r="F109" t="n">
-        <v>77303.85273470855</v>
+        <v>113076.4791728627</v>
       </c>
       <c r="G109" t="n">
-        <v>-38904.80761686389</v>
+        <v>-56908.14251276432</v>
       </c>
       <c r="H109" t="n">
-        <v>38904.80761686389</v>
+        <v>56908.14251276432</v>
       </c>
       <c r="I109" t="n">
-        <v>45.09999847412109</v>
+        <v>43.88999938964844</v>
       </c>
       <c r="J109" t="n">
-        <v>862.6343444155086</v>
+        <v>1296.608414311946</v>
       </c>
       <c r="K109" t="n">
-        <v>0.0002486041621219749</v>
+        <v>0.0003865623398658218</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0001030576548777784</v>
+        <v>0.0001507479427368688</v>
       </c>
       <c r="M109" t="n">
-        <v>0.0001020868925832682</v>
+        <v>0.0001534447645996664</v>
       </c>
       <c r="N109" t="n">
-        <v>3469911.111111111</v>
+        <v>3354202.62295082</v>
       </c>
       <c r="O109" t="n">
-        <v>156492985.8164469</v>
+        <v>147215951.0740687</v>
       </c>
       <c r="P109" t="n">
         <v>377505267.9299097</v>
@@ -6904,40 +6904,40 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.001211960583429039</v>
+        <v>0.001756582522971648</v>
       </c>
       <c r="E110" t="n">
-        <v>113621.3046964724</v>
+        <v>164679.611528592</v>
       </c>
       <c r="F110" t="n">
-        <v>75633.5732700356</v>
+        <v>109621.2325487886</v>
       </c>
       <c r="G110" t="n">
-        <v>-37987.73142643677</v>
+        <v>-55058.3789798034</v>
       </c>
       <c r="H110" t="n">
-        <v>37987.73142643677</v>
+        <v>55058.3789798034</v>
       </c>
       <c r="I110" t="n">
-        <v>28.3700008392334</v>
+        <v>28.03000068664551</v>
       </c>
       <c r="J110" t="n">
-        <v>1339.010585220105</v>
+        <v>1964.266058902923</v>
       </c>
       <c r="K110" t="n">
-        <v>0.0002409192737290103</v>
+        <v>0.0003484264516209354</v>
       </c>
       <c r="L110" t="n">
-        <v>4.424629580559106e-05</v>
+        <v>6.412937102164899e-05</v>
       </c>
       <c r="M110" t="n">
-        <v>4.550588070396683e-05</v>
+        <v>6.67550039812377e-05</v>
       </c>
       <c r="N110" t="n">
-        <v>5557922.222222222</v>
+        <v>5637534.262295082</v>
       </c>
       <c r="O110" t="n">
-        <v>157678258.1088384</v>
+        <v>158020089.2431187</v>
       </c>
       <c r="P110" t="n">
         <v>858551676.1300626</v>
@@ -6949,12 +6949,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TSLG</t>
+          <t>TARK</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6963,57 +6963,57 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.0009576260943733255</v>
+        <v>0.001725348758150231</v>
       </c>
       <c r="E111" t="n">
-        <v>89777.44634749927</v>
+        <v>161751.4460765841</v>
       </c>
       <c r="F111" t="n">
-        <v>59761.583309218</v>
+        <v>107435.983995797</v>
       </c>
       <c r="G111" t="n">
-        <v>-30015.86303828127</v>
+        <v>-54315.46208078715</v>
       </c>
       <c r="H111" t="n">
-        <v>30015.86303828127</v>
+        <v>54315.46208078715</v>
       </c>
       <c r="I111" t="n">
-        <v>7.690000057220459</v>
+        <v>48.34400177001953</v>
       </c>
       <c r="J111" t="n">
-        <v>3903.233135882506</v>
+        <v>1123.520190553832</v>
       </c>
       <c r="K111" t="n">
-        <v>7.610397781715213e-05</v>
+        <v>0.05162209452660073</v>
       </c>
       <c r="L111" t="n">
-        <v>0.0007833772272506191</v>
+        <v>0.002221662497775688</v>
       </c>
       <c r="M111" t="n">
-        <v>0.0007833771666285016</v>
+        <v>0.00217576240472875</v>
       </c>
       <c r="N111" t="n">
-        <v>51288161.9047619</v>
+        <v>21764.32786885246</v>
       </c>
       <c r="O111" t="n">
-        <v>394405967.9823512</v>
+        <v>1052174.705015089</v>
       </c>
       <c r="P111" t="n">
-        <v>38315976</v>
+        <v>24448115.83</v>
       </c>
       <c r="Q111" t="n">
-        <v>4982572</v>
+        <v>516380</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GGLL</t>
+          <t>TSLG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7022,57 +7022,57 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.0008143850947816776</v>
+        <v>0.001396888271965724</v>
       </c>
       <c r="E112" t="n">
-        <v>76348.60263578227</v>
+        <v>130958.2754967866</v>
       </c>
       <c r="F112" t="n">
-        <v>50831.02154093525</v>
+        <v>87174.16466536345</v>
       </c>
       <c r="G112" t="n">
-        <v>-25517.58109484702</v>
+        <v>-43784.11083142313</v>
       </c>
       <c r="H112" t="n">
-        <v>25517.58109484702</v>
+        <v>43784.11083142313</v>
       </c>
       <c r="I112" t="n">
-        <v>147.9700012207031</v>
+        <v>8.289999961853027</v>
       </c>
       <c r="J112" t="n">
-        <v>172.4510433488916</v>
+        <v>5281.557422545061</v>
       </c>
       <c r="K112" t="n">
-        <v>0.0001345148628156926</v>
+        <v>0.0001002419385877832</v>
       </c>
       <c r="L112" t="n">
-        <v>2.118473868848137e-05</v>
+        <v>0.001142711615421806</v>
       </c>
       <c r="M112" t="n">
-        <v>2.118473918714379e-05</v>
+        <v>0.001060006242267058</v>
       </c>
       <c r="N112" t="n">
-        <v>1282022.222222222</v>
+        <v>52688101.37704918</v>
       </c>
       <c r="O112" t="n">
-        <v>189700829.7871908</v>
+        <v>436784358.4058461</v>
       </c>
       <c r="P112" t="n">
-        <v>1204526592</v>
+        <v>38315976</v>
       </c>
       <c r="Q112" t="n">
-        <v>8140343</v>
+        <v>4982572</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ASMG</t>
+          <t>GGLL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7081,57 +7081,57 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.0004886395140282191</v>
+        <v>0.001229905017063869</v>
       </c>
       <c r="E113" t="n">
-        <v>45809.95444014554</v>
+        <v>115303.5953497377</v>
       </c>
       <c r="F113" t="n">
-        <v>30458.09303259007</v>
+        <v>76766.2974387291</v>
       </c>
       <c r="G113" t="n">
-        <v>-15351.86140755548</v>
+        <v>-38537.29791100859</v>
       </c>
       <c r="H113" t="n">
-        <v>15351.86140755548</v>
+        <v>38537.29791100859</v>
       </c>
       <c r="I113" t="n">
-        <v>44.53400039672852</v>
+        <v>139.0099945068359</v>
       </c>
       <c r="J113" t="n">
-        <v>344.7222632324589</v>
+        <v>277.2268141418672</v>
       </c>
       <c r="K113" t="n">
-        <v>0.002799044011863139</v>
+        <v>0.0002215682401914504</v>
       </c>
       <c r="L113" t="n">
-        <v>0.0004756241184610767</v>
+        <v>3.199372945932321e-05</v>
       </c>
       <c r="M113" t="n">
-        <v>0.0004756239670747344</v>
+        <v>3.405591314049877e-05</v>
       </c>
       <c r="N113" t="n">
-        <v>123157.1428571429</v>
+        <v>1251202.852459016</v>
       </c>
       <c r="O113" t="n">
-        <v>5484680.24885995</v>
+        <v>173929701.6472653</v>
       </c>
       <c r="P113" t="n">
-        <v>32277298</v>
+        <v>1204526592</v>
       </c>
       <c r="Q113" t="n">
-        <v>724779</v>
+        <v>8140343</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MSTU</t>
+          <t>ASMG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7140,57 +7140,57 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.0002661654892348791</v>
+        <v>0.0008348395336810656</v>
       </c>
       <c r="E114" t="n">
-        <v>24953.01461576992</v>
+        <v>78266.2062825999</v>
       </c>
       <c r="F114" t="n">
-        <v>16593.54573276492</v>
+        <v>52037.58487422192</v>
       </c>
       <c r="G114" t="n">
-        <v>-8359.468883004998</v>
+        <v>-26228.62140837799</v>
       </c>
       <c r="H114" t="n">
-        <v>8359.468883004998</v>
+        <v>26228.62140837799</v>
       </c>
       <c r="I114" t="n">
-        <v>8.859999656677246</v>
+        <v>43.27999877929688</v>
       </c>
       <c r="J114" t="n">
-        <v>943.5066824980034</v>
+        <v>606.0217686726121</v>
       </c>
       <c r="K114" t="n">
-        <v>2.564585035833921e-05</v>
+        <v>0.004838792919776561</v>
       </c>
       <c r="L114" t="n">
-        <v>1.099467685993012e-05</v>
+        <v>0.0008126027590158874</v>
       </c>
       <c r="M114" t="n">
-        <v>1.018807003587162e-05</v>
+        <v>0.0008361469753850651</v>
       </c>
       <c r="N114" t="n">
-        <v>36789838.0952381</v>
+        <v>125242.3442622951</v>
       </c>
       <c r="O114" t="n">
-        <v>325957952.893021</v>
+        <v>5420488.50678841</v>
       </c>
       <c r="P114" t="n">
-        <v>760319651.91</v>
+        <v>32277298</v>
       </c>
       <c r="Q114" t="n">
-        <v>92608971</v>
+        <v>724779</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SOUX</t>
+          <t>MRAL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7199,57 +7199,57 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.0001558640267008464</v>
+        <v>0.0002253998352162614</v>
       </c>
       <c r="E115" t="n">
-        <v>14612.25250320435</v>
+        <v>21131.2345515245</v>
       </c>
       <c r="F115" t="n">
-        <v>9738.252335357667</v>
+        <v>14061.56758881975</v>
       </c>
       <c r="G115" t="n">
-        <v>-4874.000167846681</v>
+        <v>-7069.666962704751</v>
       </c>
       <c r="H115" t="n">
-        <v>4874.000167846681</v>
+        <v>7069.666962704751</v>
       </c>
       <c r="I115" t="n">
-        <v>24.3700008392334</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="J115" t="n">
-        <v>200</v>
+        <v>97.39175257423889</v>
       </c>
       <c r="K115" t="n">
-        <v>0.001251791378038513</v>
+        <v>0.000580230819554711</v>
       </c>
       <c r="L115" t="n">
-        <v>0.0002280767509521142</v>
+        <v>9.557622338062932e-05</v>
       </c>
       <c r="M115" t="n">
-        <v>0.0002285756082396936</v>
+        <v>8.87006015341211e-05</v>
       </c>
       <c r="N115" t="n">
-        <v>159771.0317460317</v>
+        <v>167850.0163934426</v>
       </c>
       <c r="O115" t="n">
-        <v>3893620.17773598</v>
+        <v>12184232.07531488</v>
       </c>
       <c r="P115" t="n">
-        <v>21370000</v>
+        <v>73968888</v>
       </c>
       <c r="Q115" t="n">
-        <v>874984</v>
+        <v>1097983</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CRWL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7258,57 +7258,57 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.739659656306519e-05</v>
+        <v>0.0001947683340698242</v>
       </c>
       <c r="E116" t="n">
-        <v>6318.430927787362</v>
+        <v>18259.53131904602</v>
       </c>
       <c r="F116" t="n">
-        <v>4210.179033297084</v>
+        <v>12146.53121223449</v>
       </c>
       <c r="G116" t="n">
-        <v>-2108.251894490278</v>
+        <v>-6113.000106811523</v>
       </c>
       <c r="H116" t="n">
-        <v>2108.251894490278</v>
+        <v>6113.000106811523</v>
       </c>
       <c r="I116" t="n">
-        <v>32.86399841308594</v>
+        <v>61.13000106811523</v>
       </c>
       <c r="J116" t="n">
-        <v>64.15080319778752</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="K116" t="n">
-        <v>0.0001980642294271313</v>
+        <v>0.0002247873115890793</v>
       </c>
       <c r="L116" t="n">
-        <v>3.751529414552962e-05</v>
+        <v>3.075617915521461e-05</v>
       </c>
       <c r="M116" t="n">
-        <v>3.751506765071338e-05</v>
+        <v>3.100774232318067e-05</v>
       </c>
       <c r="N116" t="n">
-        <v>323888.8888888889</v>
+        <v>444864.9672131148</v>
       </c>
       <c r="O116" t="n">
-        <v>10644283.93046061</v>
+        <v>27194595.92090476</v>
       </c>
       <c r="P116" t="n">
-        <v>56197130.8638</v>
+        <v>198756811.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>1710001</v>
+        <v>3225001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MRAL</t>
+          <t>MSTU</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7317,46 +7317,105 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.716944667247781e-05</v>
+        <v>4.314011310395495e-05</v>
       </c>
       <c r="E117" t="n">
-        <v>2547.135625544795</v>
+        <v>4044.385603495777</v>
       </c>
       <c r="F117" t="n">
-        <v>1694.965794315355</v>
+        <v>2689.482553748448</v>
       </c>
       <c r="G117" t="n">
-        <v>-852.1698312294396</v>
+        <v>-1354.903049747329</v>
       </c>
       <c r="H117" t="n">
-        <v>852.1698312294396</v>
+        <v>1354.903049747329</v>
       </c>
       <c r="I117" t="n">
-        <v>67.36799621582031</v>
+        <v>9.630000114440918</v>
       </c>
       <c r="J117" t="n">
-        <v>12.64947570207411</v>
+        <v>140.6960574917905</v>
       </c>
       <c r="K117" t="n">
-        <v>7.595718592011835e-05</v>
+        <v>3.875398288628514e-06</v>
       </c>
       <c r="L117" t="n">
-        <v>1.152065218594931e-05</v>
+        <v>1.782017663680894e-06</v>
       </c>
       <c r="M117" t="n">
-        <v>1.152064804470935e-05</v>
+        <v>1.519248685872889e-06</v>
       </c>
       <c r="N117" t="n">
-        <v>166534.2857142857</v>
+        <v>36304928.42622951</v>
       </c>
       <c r="O117" t="n">
-        <v>11219081.12980434</v>
+        <v>349616464.8993595</v>
       </c>
       <c r="P117" t="n">
-        <v>73968888</v>
+        <v>760319651.91</v>
       </c>
       <c r="Q117" t="n">
-        <v>1097983</v>
+        <v>92608971</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CRWL</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>core_leveraged</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3.303928958553888e-05</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3097.433398644271</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2063.922087785321</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-1033.511310858949</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1033.511310858949</v>
+      </c>
+      <c r="I118" t="n">
+        <v>34.7599983215332</v>
+      </c>
+      <c r="J118" t="n">
+        <v>29.73277792763031</v>
+      </c>
+      <c r="K118" t="n">
+        <v>9.006476419682208e-05</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1.839081986878972e-05</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.738757926318775e-05</v>
+      </c>
+      <c r="N118" t="n">
+        <v>330126.6393442623</v>
+      </c>
+      <c r="O118" t="n">
+        <v>11475201.42949996</v>
+      </c>
+      <c r="P118" t="n">
+        <v>56197130.8638</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1710001</v>
       </c>
     </row>
   </sheetData>
